--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -718,16 +718,16 @@
     <t>2021-07-07</t>
   </si>
   <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
     <t>2021-07-06</t>
   </si>
   <si>
-    <t>2021-07-16</t>
+    <t>2021-06-04</t>
   </si>
   <si>
     <t>2021-04-01</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
   </si>
   <si>
     <t>2016-06-02</t>
@@ -1078,7 +1078,7 @@
     <t>2021-08-18</t>
   </si>
   <si>
-    <t>2021-04-12</t>
+    <t>2021-08-23</t>
   </si>
   <si>
     <t>2016-04-14</t>
@@ -71590,10 +71590,10 @@
         <v>-0.8045747150302098</v>
       </c>
       <c r="D1396" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E1396">
-        <v>-1.080811452774951</v>
+        <v>-1.220352677366442</v>
       </c>
       <c r="F1396">
         <v>-1</v>
@@ -71602,10 +71602,10 @@
         <v>0.00732457471503021</v>
       </c>
       <c r="H1396">
-        <v>0.008220811452774951</v>
+        <v>0.008120352677366443</v>
       </c>
       <c r="I1396">
-        <v>0.2762367377447412</v>
+        <v>0.4157779623362323</v>
       </c>
       <c r="J1396">
         <v>1.954122459149139</v>
@@ -71617,10 +71617,10 @@
         <v>3.26</v>
       </c>
       <c r="M1396">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="N1396">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="O1396">
         <v>1</v>
@@ -71640,10 +71640,10 @@
         <v>-0.7700800199323123</v>
       </c>
       <c r="D1397" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E1397">
-        <v>-1.080811452774951</v>
+        <v>-1.220352677366442</v>
       </c>
       <c r="F1397">
         <v>-1</v>
@@ -71652,10 +71652,10 @@
         <v>0.006890080019932313</v>
       </c>
       <c r="H1397">
-        <v>0.008220811452774951</v>
+        <v>0.008120352677366443</v>
       </c>
       <c r="I1397">
-        <v>0.3107314328426387</v>
+        <v>0.4502726574341298</v>
       </c>
       <c r="J1397">
         <v>1.954122459149139</v>
@@ -71667,10 +71667,10 @@
         <v>3.06</v>
       </c>
       <c r="M1397">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="N1397">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="O1397">
         <v>1</v>
@@ -71690,10 +71690,10 @@
         <v>-0.8027396133961755</v>
       </c>
       <c r="D1398" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E1398">
-        <v>-1.080811452774951</v>
+        <v>-1.220352677366442</v>
       </c>
       <c r="F1398">
         <v>-1</v>
@@ -71702,10 +71702,10 @@
         <v>0.007482739613396175</v>
       </c>
       <c r="H1398">
-        <v>0.008220811452774951</v>
+        <v>0.008120352677366443</v>
       </c>
       <c r="I1398">
-        <v>0.2780718393787756</v>
+        <v>0.4176130639702667</v>
       </c>
       <c r="J1398">
         <v>1.954122459149139</v>
@@ -71717,10 +71717,10 @@
         <v>3.34</v>
       </c>
       <c r="M1398">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="N1398">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="O1398">
         <v>1</v>
@@ -71784,43 +71784,43 @@
         <v>4</v>
       </c>
       <c r="B1400" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C1400">
-        <v>-0.762280837987666</v>
+        <v>-1.416682474098374</v>
       </c>
       <c r="D1400" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1400">
-        <v>-1.099986960945123</v>
+        <v>-0.9572343084940718</v>
       </c>
       <c r="F1400">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1400">
-        <v>0.007562280837987666</v>
+        <v>0.008236682474098374</v>
       </c>
       <c r="H1400">
-        <v>0.007419986960945124</v>
+        <v>0.007797234308494072</v>
       </c>
       <c r="I1400">
-        <v>0.3377061229574569</v>
+        <v>0.4594481656043019</v>
       </c>
       <c r="J1400">
         <v>1.954122459149139</v>
       </c>
       <c r="K1400">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="L1400">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="M1400">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="N1400">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="O1400">
         <v>1</v>
@@ -71834,10 +71834,10 @@
         <v>5</v>
       </c>
       <c r="B1401" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C1401">
-        <v>-0.7709045117621409</v>
+        <v>-0.8104457363536315</v>
       </c>
       <c r="D1401" t="s">
         <v>348</v>
@@ -71849,22 +71849,22 @@
         <v>-1</v>
       </c>
       <c r="G1401">
-        <v>0.007670904511762141</v>
+        <v>0.007670445736353631</v>
       </c>
       <c r="H1401">
         <v>0.007419986960945124</v>
       </c>
       <c r="I1401">
-        <v>0.329082449182982</v>
+        <v>0.2895412245914915</v>
       </c>
       <c r="J1401">
         <v>1.954122459149139</v>
       </c>
       <c r="K1401">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="L1401">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="M1401">
         <v>2.18</v>
@@ -71884,10 +71884,10 @@
         <v>6</v>
       </c>
       <c r="B1402" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C1402">
-        <v>-0.7804457363536317</v>
+        <v>-0.7709045117621409</v>
       </c>
       <c r="D1402" t="s">
         <v>348</v>
@@ -71899,22 +71899,22 @@
         <v>-1</v>
       </c>
       <c r="G1402">
-        <v>0.007700445736353632</v>
+        <v>0.007670904511762141</v>
       </c>
       <c r="H1402">
         <v>0.007419986960945124</v>
       </c>
       <c r="I1402">
-        <v>0.3195412245914913</v>
+        <v>0.329082449182982</v>
       </c>
       <c r="J1402">
         <v>1.954122459149139</v>
       </c>
       <c r="K1402">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="L1402">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="M1402">
         <v>2.18</v>
@@ -71934,43 +71934,43 @@
         <v>7</v>
       </c>
       <c r="B1403" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C1403">
-        <v>-1.398517575732408</v>
+        <v>-0.7804457363536317</v>
       </c>
       <c r="D1403" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1403">
-        <v>-1.200811452774951</v>
+        <v>-1.099986960945123</v>
       </c>
       <c r="F1403">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1403">
-        <v>0.008098517575732409</v>
+        <v>0.007700445736353632</v>
       </c>
       <c r="H1403">
-        <v>0.008100811452774952</v>
+        <v>0.007419986960945124</v>
       </c>
       <c r="I1403">
-        <v>0.1977061229574573</v>
+        <v>0.3195412245914913</v>
       </c>
       <c r="J1403">
         <v>1.954122459149139</v>
       </c>
       <c r="K1403">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="L1403">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="M1403">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1403">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1403">
         <v>1</v>
@@ -71981,63 +71981,63 @@
     </row>
     <row r="1404" spans="1:16">
       <c r="A1404" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1404" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C1404">
-        <v>-0.3780353550827891</v>
+        <v>-1.398517575732408</v>
       </c>
       <c r="D1404" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1404">
-        <v>-0.7422982135958502</v>
+        <v>-1.603836762660132</v>
       </c>
       <c r="F1404">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1404">
-        <v>0.00649803535508279</v>
+        <v>0.008098517575732409</v>
       </c>
       <c r="H1404">
-        <v>0.007642298213595851</v>
+        <v>0.009143836762660134</v>
       </c>
       <c r="I1404">
-        <v>0.3642628585130612</v>
+        <v>-0.2053191869277242</v>
       </c>
       <c r="J1404">
-        <v>1.754099670960607</v>
+        <v>1.954122459149139</v>
       </c>
       <c r="K1404">
-        <v>1.96</v>
+        <v>2.43</v>
       </c>
       <c r="L1404">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="M1404">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1404">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1404">
         <v>1</v>
       </c>
       <c r="P1404" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1405" spans="1:16">
       <c r="A1405" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1405" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C1405">
-        <v>-0.3786913024364864</v>
+        <v>-0.3780353550827891</v>
       </c>
       <c r="D1405" t="s">
         <v>346</v>
@@ -72049,22 +72049,22 @@
         <v>-1</v>
       </c>
       <c r="G1405">
-        <v>0.007058691302436486</v>
+        <v>0.00649803535508279</v>
       </c>
       <c r="H1405">
         <v>0.007642298213595851</v>
       </c>
       <c r="I1405">
-        <v>0.3636069111593638</v>
+        <v>0.3642628585130612</v>
       </c>
       <c r="J1405">
         <v>1.754099670960607</v>
       </c>
       <c r="K1405">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="L1405">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="M1405">
         <v>2.39</v>
@@ -72081,46 +72081,46 @@
     </row>
     <row r="1406" spans="1:16">
       <c r="A1406" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1406" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1406">
-        <v>-0.8875441938534863</v>
+        <v>-0.3786913024364864</v>
       </c>
       <c r="D1406" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1406">
-        <v>-0.5091832629517596</v>
+        <v>-0.7422982135958502</v>
       </c>
       <c r="F1406">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1406">
-        <v>0.007707544193853486</v>
+        <v>0.007058691302436486</v>
       </c>
       <c r="H1406">
-        <v>0.00734918326295176</v>
+        <v>0.007642298213595851</v>
       </c>
       <c r="I1406">
-        <v>0.3783609309017266</v>
+        <v>0.3636069111593638</v>
       </c>
       <c r="J1406">
         <v>1.754099670960607</v>
       </c>
       <c r="K1406">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="L1406">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="M1406">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1406">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1406">
         <v>1</v>
@@ -72131,13 +72131,13 @@
     </row>
     <row r="1407" spans="1:16">
       <c r="A1407" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1407" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C1407">
-        <v>-0.9226261872726988</v>
+        <v>-0.8875441938534863</v>
       </c>
       <c r="D1407" t="s">
         <v>347</v>
@@ -72149,19 +72149,19 @@
         <v>1</v>
       </c>
       <c r="G1407">
-        <v>0.007742626187272699</v>
+        <v>0.007707544193853486</v>
       </c>
       <c r="H1407">
         <v>0.00734918326295176</v>
       </c>
       <c r="I1407">
-        <v>0.4134429243209392</v>
+        <v>0.3783609309017266</v>
       </c>
       <c r="J1407">
         <v>1.754099670960607</v>
       </c>
       <c r="K1407">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="L1407">
         <v>3.41</v>
@@ -72181,46 +72181,46 @@
     </row>
     <row r="1408" spans="1:16">
       <c r="A1408" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1408" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C1408">
-        <v>-0.3763962859845162</v>
+        <v>-0.9226261872726988</v>
       </c>
       <c r="D1408" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1408">
-        <v>-0.6639372826941226</v>
+        <v>-0.5091832629517596</v>
       </c>
       <c r="F1408">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1408">
-        <v>0.007236396285984517</v>
+        <v>0.007742626187272699</v>
       </c>
       <c r="H1408">
-        <v>0.006983937282694123</v>
+        <v>0.00734918326295176</v>
       </c>
       <c r="I1408">
-        <v>0.2875409967096063</v>
+        <v>0.4134429243209392</v>
       </c>
       <c r="J1408">
         <v>1.754099670960607</v>
       </c>
       <c r="K1408">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="L1408">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="M1408">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="N1408">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="O1408">
         <v>1</v>
@@ -72231,13 +72231,13 @@
     </row>
     <row r="1409" spans="1:16">
       <c r="A1409" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1409" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C1409">
-        <v>-0.3463962859845164</v>
+        <v>-0.3763962859845162</v>
       </c>
       <c r="D1409" t="s">
         <v>348</v>
@@ -72249,13 +72249,13 @@
         <v>-1</v>
       </c>
       <c r="G1409">
-        <v>0.007266396285984517</v>
+        <v>0.007236396285984517</v>
       </c>
       <c r="H1409">
         <v>0.006983937282694123</v>
       </c>
       <c r="I1409">
-        <v>0.3175409967096061</v>
+        <v>0.2875409967096063</v>
       </c>
       <c r="J1409">
         <v>1.754099670960607</v>
@@ -72264,7 +72264,7 @@
         <v>2.17</v>
       </c>
       <c r="L1409">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="M1409">
         <v>2.18</v>
@@ -72281,46 +72281,46 @@
     </row>
     <row r="1410" spans="1:16">
       <c r="A1410" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1410" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C1410">
-        <v>-0.9124622004342746</v>
+        <v>-0.3463962859845164</v>
       </c>
       <c r="D1410" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1410">
-        <v>-0.7247572168862435</v>
+        <v>-0.6639372826941226</v>
       </c>
       <c r="F1410">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1410">
-        <v>0.007612462200434275</v>
+        <v>0.007266396285984517</v>
       </c>
       <c r="H1410">
-        <v>0.007624757216886244</v>
+        <v>0.006983937282694123</v>
       </c>
       <c r="I1410">
-        <v>0.1877049835480311</v>
+        <v>0.3175409967096061</v>
       </c>
       <c r="J1410">
         <v>1.754099670960607</v>
       </c>
       <c r="K1410">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="L1410">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="M1410">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1410">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1410">
         <v>1</v>
@@ -72331,63 +72331,63 @@
     </row>
     <row r="1411" spans="1:16">
       <c r="A1411" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1411" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C1411">
-        <v>-0.2073562023747662</v>
+        <v>-0.9124622004342746</v>
       </c>
       <c r="D1411" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1411">
-        <v>-0.5341741447324955</v>
+        <v>-1.053774095141668</v>
       </c>
       <c r="F1411">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1411">
-        <v>0.006327356202374766</v>
+        <v>0.007612462200434275</v>
       </c>
       <c r="H1411">
-        <v>0.007434174144732496</v>
+        <v>0.008593774095141669</v>
       </c>
       <c r="I1411">
-        <v>0.3268179423577293</v>
+        <v>-0.1413118947073935</v>
       </c>
       <c r="J1411">
-        <v>1.66701847059937</v>
+        <v>1.754099670960607</v>
       </c>
       <c r="K1411">
-        <v>1.96</v>
+        <v>2.43</v>
       </c>
       <c r="L1411">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="M1411">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1411">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1411">
         <v>1</v>
       </c>
       <c r="P1411" t="s">
-        <v>211</v>
+        <v>479</v>
       </c>
     </row>
     <row r="1412" spans="1:16">
       <c r="A1412" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1412" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C1412">
-        <v>-0.1940791576706657</v>
+        <v>-0.2073562023747662</v>
       </c>
       <c r="D1412" t="s">
         <v>346</v>
@@ -72399,22 +72399,22 @@
         <v>-1</v>
       </c>
       <c r="G1412">
-        <v>0.006874079157670666</v>
+        <v>0.006327356202374766</v>
       </c>
       <c r="H1412">
         <v>0.007434174144732496</v>
       </c>
       <c r="I1412">
-        <v>0.3400949870618297</v>
+        <v>0.3268179423577293</v>
       </c>
       <c r="J1412">
         <v>1.66701847059937</v>
       </c>
       <c r="K1412">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="L1412">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="M1412">
         <v>2.39</v>
@@ -72431,46 +72431,46 @@
     </row>
     <row r="1413" spans="1:16">
       <c r="A1413" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1413" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1413">
-        <v>-0.6741952529684578</v>
+        <v>-0.1940791576706657</v>
       </c>
       <c r="D1413" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1413">
-        <v>-0.3141213741425903</v>
+        <v>-0.5341741447324955</v>
       </c>
       <c r="F1413">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1413">
-        <v>0.007494195252968458</v>
+        <v>0.006874079157670666</v>
       </c>
       <c r="H1413">
-        <v>0.00715412137414259</v>
+        <v>0.007434174144732496</v>
       </c>
       <c r="I1413">
-        <v>0.3600738788258675</v>
+        <v>0.3400949870618297</v>
       </c>
       <c r="J1413">
         <v>1.66701847059937</v>
       </c>
       <c r="K1413">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="L1413">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="M1413">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1413">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1413">
         <v>1</v>
@@ -72481,13 +72481,13 @@
     </row>
     <row r="1414" spans="1:16">
       <c r="A1414" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1414" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C1414">
-        <v>-0.707535622380445</v>
+        <v>-0.6741952529684578</v>
       </c>
       <c r="D1414" t="s">
         <v>347</v>
@@ -72499,19 +72499,19 @@
         <v>1</v>
       </c>
       <c r="G1414">
-        <v>0.007527535622380445</v>
+        <v>0.007494195252968458</v>
       </c>
       <c r="H1414">
         <v>0.00715412137414259</v>
       </c>
       <c r="I1414">
-        <v>0.3934142482378546</v>
+        <v>0.3600738788258675</v>
       </c>
       <c r="J1414">
         <v>1.66701847059937</v>
       </c>
       <c r="K1414">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="L1414">
         <v>3.41</v>
@@ -72531,46 +72531,46 @@
     </row>
     <row r="1415" spans="1:16">
       <c r="A1415" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1415" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C1415">
-        <v>-0.1874300812006338</v>
+        <v>-0.707535622380445</v>
       </c>
       <c r="D1415" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1415">
-        <v>-0.4741002659066278</v>
+        <v>-0.3141213741425903</v>
       </c>
       <c r="F1415">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1415">
-        <v>0.007047430081200634</v>
+        <v>0.007527535622380445</v>
       </c>
       <c r="H1415">
-        <v>0.006794100265906628</v>
+        <v>0.00715412137414259</v>
       </c>
       <c r="I1415">
-        <v>0.286670184705994</v>
+        <v>0.3934142482378546</v>
       </c>
       <c r="J1415">
         <v>1.66701847059937</v>
       </c>
       <c r="K1415">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="L1415">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="M1415">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="N1415">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="O1415">
         <v>1</v>
@@ -72581,13 +72581,13 @@
     </row>
     <row r="1416" spans="1:16">
       <c r="A1416" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1416" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C1416">
-        <v>-0.157430081200634</v>
+        <v>-0.1874300812006338</v>
       </c>
       <c r="D1416" t="s">
         <v>348</v>
@@ -72599,13 +72599,13 @@
         <v>-1</v>
       </c>
       <c r="G1416">
-        <v>0.007077430081200634</v>
+        <v>0.007047430081200634</v>
       </c>
       <c r="H1416">
         <v>0.006794100265906628</v>
       </c>
       <c r="I1416">
-        <v>0.3166701847059938</v>
+        <v>0.286670184705994</v>
       </c>
       <c r="J1416">
         <v>1.66701847059937</v>
@@ -72614,7 +72614,7 @@
         <v>2.17</v>
       </c>
       <c r="L1416">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="M1416">
         <v>2.18</v>
@@ -72631,46 +72631,46 @@
     </row>
     <row r="1417" spans="1:16">
       <c r="A1417" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1417" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1417">
-        <v>-0.7008548835564707</v>
+        <v>-0.2107704506126211</v>
       </c>
       <c r="D1417" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1417">
-        <v>-0.5175039600265015</v>
+        <v>-0.4741002659066278</v>
       </c>
       <c r="F1417">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1417">
-        <v>0.007400854883556471</v>
+        <v>0.007090770450612622</v>
       </c>
       <c r="H1417">
-        <v>0.007417503960026502</v>
+        <v>0.006794100265906628</v>
       </c>
       <c r="I1417">
-        <v>0.1833509235299693</v>
+        <v>0.2633298152940067</v>
       </c>
       <c r="J1417">
         <v>1.66701847059937</v>
       </c>
       <c r="K1417">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="L1417">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M1417">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1417">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1417">
         <v>1</v>
@@ -72681,96 +72681,96 @@
     </row>
     <row r="1418" spans="1:16">
       <c r="A1418" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1418" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1418">
-        <v>-0.08362420353382438</v>
+        <v>-0.7008548835564707</v>
       </c>
       <c r="D1418" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1418">
-        <v>-0.4096518143612453</v>
+        <v>-0.8143007941482687</v>
       </c>
       <c r="F1418">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1418">
-        <v>0.006763624203533825</v>
+        <v>0.007400854883556471</v>
       </c>
       <c r="H1418">
-        <v>0.007309651814361245</v>
+        <v>0.00835430079414827</v>
       </c>
       <c r="I1418">
-        <v>0.3260276108274209</v>
+        <v>-0.113445910591798</v>
       </c>
       <c r="J1418">
-        <v>1.614917077138596</v>
+        <v>1.66701847059937</v>
       </c>
       <c r="K1418">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1418">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1418">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1418">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1418">
         <v>1</v>
       </c>
       <c r="P1418" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="1419" spans="1:16">
       <c r="A1419" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1419" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1419">
-        <v>-0.5465468389895611</v>
+        <v>-0.08362420353382438</v>
       </c>
       <c r="D1419" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1419">
-        <v>-0.1974142527904563</v>
+        <v>-0.4096518143612453</v>
       </c>
       <c r="F1419">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1419">
-        <v>0.007366546838989562</v>
+        <v>0.006763624203533825</v>
       </c>
       <c r="H1419">
-        <v>0.007037414252790457</v>
+        <v>0.007309651814361245</v>
       </c>
       <c r="I1419">
-        <v>0.3491325861991048</v>
+        <v>0.3260276108274209</v>
       </c>
       <c r="J1419">
         <v>1.614917077138596</v>
       </c>
       <c r="K1419">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="L1419">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="M1419">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1419">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1419">
         <v>1</v>
@@ -72781,13 +72781,13 @@
     </row>
     <row r="1420" spans="1:16">
       <c r="A1420" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1420" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C1420">
-        <v>-0.5788451805323329</v>
+        <v>-0.5465468389895611</v>
       </c>
       <c r="D1420" t="s">
         <v>347</v>
@@ -72799,19 +72799,19 @@
         <v>1</v>
       </c>
       <c r="G1420">
-        <v>0.007398845180532334</v>
+        <v>0.007366546838989562</v>
       </c>
       <c r="H1420">
         <v>0.007037414252790457</v>
       </c>
       <c r="I1420">
-        <v>0.3814309277418766</v>
+        <v>0.3491325861991048</v>
       </c>
       <c r="J1420">
         <v>1.614917077138596</v>
       </c>
       <c r="K1420">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="L1420">
         <v>3.41</v>
@@ -72831,46 +72831,46 @@
     </row>
     <row r="1421" spans="1:16">
       <c r="A1421" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1421" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1421">
-        <v>-0.1005192281621405</v>
+        <v>-0.5788451805323329</v>
       </c>
       <c r="D1421" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1421">
-        <v>-0.3605192281621403</v>
+        <v>-0.1974142527904563</v>
       </c>
       <c r="F1421">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1421">
-        <v>0.00694051922816214</v>
+        <v>0.007398845180532334</v>
       </c>
       <c r="H1421">
-        <v>0.00668051922816214</v>
+        <v>0.007037414252790457</v>
       </c>
       <c r="I1421">
-        <v>0.2599999999999998</v>
+        <v>0.3814309277418766</v>
       </c>
       <c r="J1421">
         <v>1.614917077138596</v>
       </c>
       <c r="K1421">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1421">
+        <v>3.41</v>
+      </c>
+      <c r="M1421">
+        <v>2.24</v>
+      </c>
+      <c r="N1421">
         <v>3.42</v>
-      </c>
-      <c r="M1421">
-        <v>2.18</v>
-      </c>
-      <c r="N1421">
-        <v>3.16</v>
       </c>
       <c r="O1421">
         <v>1</v>
@@ -72881,13 +72881,13 @@
     </row>
     <row r="1422" spans="1:16">
       <c r="A1422" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1422" t="s">
         <v>235</v>
       </c>
       <c r="C1422">
-        <v>-0.09666839893352597</v>
+        <v>-0.1005192281621405</v>
       </c>
       <c r="D1422" t="s">
         <v>348</v>
@@ -72899,22 +72899,22 @@
         <v>-1</v>
       </c>
       <c r="G1422">
-        <v>0.006976668398933526</v>
+        <v>0.00694051922816214</v>
       </c>
       <c r="H1422">
         <v>0.00668051922816214</v>
       </c>
       <c r="I1422">
-        <v>0.2638508292286144</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1422">
         <v>1.614917077138596</v>
       </c>
       <c r="K1422">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="L1422">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="M1422">
         <v>2.18</v>
@@ -72931,46 +72931,46 @@
     </row>
     <row r="1423" spans="1:16">
       <c r="A1423" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1423" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1423">
-        <v>-0.5742484974467894</v>
+        <v>-0.09666839893352597</v>
       </c>
       <c r="D1423" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1423">
-        <v>-0.393502643589859</v>
+        <v>-0.3605192281621403</v>
       </c>
       <c r="F1423">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1423">
-        <v>0.00727424849744679</v>
+        <v>0.006976668398933526</v>
       </c>
       <c r="H1423">
-        <v>0.007293502643589859</v>
+        <v>0.00668051922816214</v>
       </c>
       <c r="I1423">
-        <v>0.1807458538569304</v>
+        <v>0.2638508292286144</v>
       </c>
       <c r="J1423">
         <v>1.614917077138596</v>
       </c>
       <c r="K1423">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="L1423">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M1423">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1423">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1423">
         <v>1</v>
@@ -72981,96 +72981,96 @@
     </row>
     <row r="1424" spans="1:16">
       <c r="A1424" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1424" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1424">
-        <v>0.06222467917078056</v>
+        <v>-0.5742484974467894</v>
       </c>
       <c r="D1424" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1424">
-        <v>-0.2452278381046384</v>
+        <v>-0.6710219621311402</v>
       </c>
       <c r="F1424">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1424">
-        <v>0.006617775320829219</v>
+        <v>0.00727424849744679</v>
       </c>
       <c r="H1424">
-        <v>0.007145227838104638</v>
+        <v>0.008211021962131139</v>
       </c>
       <c r="I1424">
-        <v>0.307452517275419</v>
+        <v>-0.09677346468435077</v>
       </c>
       <c r="J1424">
-        <v>1.546120434353405</v>
+        <v>1.614917077138596</v>
       </c>
       <c r="K1424">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1424">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1424">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1424">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1424">
         <v>1</v>
       </c>
       <c r="P1424" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="1425" spans="1:16">
       <c r="A1425" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1425" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1425">
-        <v>-0.3779950641658427</v>
+        <v>0.06222467917078056</v>
       </c>
       <c r="D1425" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1425">
-        <v>-0.04330977295162786</v>
+        <v>-0.2452278381046384</v>
       </c>
       <c r="F1425">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1425">
-        <v>0.007197995064165843</v>
+        <v>0.006617775320829219</v>
       </c>
       <c r="H1425">
-        <v>0.006883309772951628</v>
+        <v>0.007145227838104638</v>
       </c>
       <c r="I1425">
-        <v>0.3346852912142149</v>
+        <v>0.307452517275419</v>
       </c>
       <c r="J1425">
         <v>1.546120434353405</v>
       </c>
       <c r="K1425">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="L1425">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="M1425">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1425">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1425">
         <v>1</v>
@@ -73081,13 +73081,13 @@
     </row>
     <row r="1426" spans="1:16">
       <c r="A1426" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1426" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C1426">
-        <v>-0.4089174728529108</v>
+        <v>-0.3779950641658427</v>
       </c>
       <c r="D1426" t="s">
         <v>347</v>
@@ -73099,19 +73099,19 @@
         <v>1</v>
       </c>
       <c r="G1426">
-        <v>0.007228917472852912</v>
+        <v>0.007197995064165843</v>
       </c>
       <c r="H1426">
         <v>0.006883309772951628</v>
       </c>
       <c r="I1426">
-        <v>0.3656076999012829</v>
+        <v>0.3346852912142149</v>
       </c>
       <c r="J1426">
         <v>1.546120434353405</v>
       </c>
       <c r="K1426">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="L1426">
         <v>3.41</v>
@@ -73131,46 +73131,46 @@
     </row>
     <row r="1427" spans="1:16">
       <c r="A1427" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1427" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1427">
-        <v>0.04945745310957639</v>
+        <v>-0.4089174728529108</v>
       </c>
       <c r="D1427" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1427">
-        <v>-0.2105425468904234</v>
+        <v>-0.04330977295162786</v>
       </c>
       <c r="F1427">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1427">
-        <v>0.006790542546890423</v>
+        <v>0.007228917472852912</v>
       </c>
       <c r="H1427">
-        <v>0.006530542546890423</v>
+        <v>0.006883309772951628</v>
       </c>
       <c r="I1427">
-        <v>0.2599999999999998</v>
+        <v>0.3656076999012829</v>
       </c>
       <c r="J1427">
         <v>1.546120434353405</v>
       </c>
       <c r="K1427">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1427">
+        <v>3.41</v>
+      </c>
+      <c r="M1427">
+        <v>2.24</v>
+      </c>
+      <c r="N1427">
         <v>3.42</v>
-      </c>
-      <c r="M1427">
-        <v>2.18</v>
-      </c>
-      <c r="N1427">
-        <v>3.16</v>
       </c>
       <c r="O1427">
         <v>1</v>
@@ -73181,13 +73181,13 @@
     </row>
     <row r="1428" spans="1:16">
       <c r="A1428" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1428" t="s">
         <v>235</v>
       </c>
       <c r="C1428">
-        <v>0.05399624876604259</v>
+        <v>0.04945745310957639</v>
       </c>
       <c r="D1428" t="s">
         <v>348</v>
@@ -73199,22 +73199,22 @@
         <v>-1</v>
       </c>
       <c r="G1428">
-        <v>0.006826003751233957</v>
+        <v>0.006790542546890423</v>
       </c>
       <c r="H1428">
         <v>0.006530542546890423</v>
       </c>
       <c r="I1428">
-        <v>0.264538795656466</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1428">
         <v>1.546120434353405</v>
       </c>
       <c r="K1428">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="L1428">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="M1428">
         <v>2.18</v>
@@ -73231,46 +73231,46 @@
     </row>
     <row r="1429" spans="1:16">
       <c r="A1429" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1429" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1429">
-        <v>-0.4070726554787747</v>
+        <v>0.05399624876604259</v>
       </c>
       <c r="D1429" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1429">
-        <v>-0.2297666337611042</v>
+        <v>-0.2105425468904234</v>
       </c>
       <c r="F1429">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1429">
-        <v>0.007107072655478775</v>
+        <v>0.006826003751233957</v>
       </c>
       <c r="H1429">
-        <v>0.007129766633761104</v>
+        <v>0.006530542546890423</v>
       </c>
       <c r="I1429">
-        <v>0.1773060217176705</v>
+        <v>0.264538795656466</v>
       </c>
       <c r="J1429">
         <v>1.546120434353405</v>
       </c>
       <c r="K1429">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="L1429">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M1429">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1429">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1429">
         <v>1</v>
@@ -73281,96 +73281,96 @@
     </row>
     <row r="1430" spans="1:16">
       <c r="A1430" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1430" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1430">
-        <v>0.1846987262292132</v>
+        <v>-0.4070726554787747</v>
       </c>
       <c r="D1430" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1430">
-        <v>-0.10715568127933</v>
+        <v>-0.4818311944718645</v>
       </c>
       <c r="F1430">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1430">
-        <v>0.006495301273770787</v>
+        <v>0.007107072655478775</v>
       </c>
       <c r="H1430">
-        <v>0.007007155681279331</v>
+        <v>0.008021831194471866</v>
       </c>
       <c r="I1430">
-        <v>0.2918544075085432</v>
+        <v>-0.07475853899308982</v>
       </c>
       <c r="J1430">
-        <v>1.48834965743905</v>
+        <v>1.546120434353405</v>
       </c>
       <c r="K1430">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1430">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1430">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1430">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1430">
         <v>1</v>
       </c>
       <c r="P1430" t="s">
-        <v>480</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1431" spans="1:16">
       <c r="A1431" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1431" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1431">
-        <v>-0.2364566607256733</v>
+        <v>0.1846987262292132</v>
       </c>
       <c r="D1431" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1431">
-        <v>0.08609676733652716</v>
+        <v>-0.10715568127933</v>
       </c>
       <c r="F1431">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1431">
-        <v>0.007056456660725674</v>
+        <v>0.006495301273770787</v>
       </c>
       <c r="H1431">
-        <v>0.006753903232663473</v>
+        <v>0.007007155681279331</v>
       </c>
       <c r="I1431">
-        <v>0.3225534280622004</v>
+        <v>0.2918544075085432</v>
       </c>
       <c r="J1431">
         <v>1.48834965743905</v>
       </c>
       <c r="K1431">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="L1431">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="M1431">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1431">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1431">
         <v>1</v>
@@ -73381,13 +73381,13 @@
     </row>
     <row r="1432" spans="1:16">
       <c r="A1432" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1432" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C1432">
-        <v>-0.2662236538744542</v>
+        <v>-0.2762236538744545</v>
       </c>
       <c r="D1432" t="s">
         <v>347</v>
@@ -73399,13 +73399,13 @@
         <v>1</v>
       </c>
       <c r="G1432">
-        <v>0.007086223653874455</v>
+        <v>0.007076223653874454</v>
       </c>
       <c r="H1432">
         <v>0.006753903232663473</v>
       </c>
       <c r="I1432">
-        <v>0.3523204212109814</v>
+        <v>0.3623204212109816</v>
       </c>
       <c r="J1432">
         <v>1.48834965743905</v>
@@ -73414,7 +73414,7 @@
         <v>2.47</v>
       </c>
       <c r="L1432">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="M1432">
         <v>2.24</v>
@@ -73431,46 +73431,46 @@
     </row>
     <row r="1433" spans="1:16">
       <c r="A1433" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1433" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1433">
-        <v>0.17539774678287</v>
+        <v>-0.2662236538744542</v>
       </c>
       <c r="D1433" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1433">
-        <v>-0.08460225321712977</v>
+        <v>0.08609676733652716</v>
       </c>
       <c r="F1433">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1433">
-        <v>0.00666460225321713</v>
+        <v>0.007086223653874455</v>
       </c>
       <c r="H1433">
-        <v>0.00640460225321713</v>
+        <v>0.006753903232663473</v>
       </c>
       <c r="I1433">
-        <v>0.2599999999999998</v>
+        <v>0.3523204212109814</v>
       </c>
       <c r="J1433">
         <v>1.48834965743905</v>
       </c>
       <c r="K1433">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1433">
+        <v>3.41</v>
+      </c>
+      <c r="M1433">
+        <v>2.24</v>
+      </c>
+      <c r="N1433">
         <v>3.42</v>
-      </c>
-      <c r="M1433">
-        <v>2.18</v>
-      </c>
-      <c r="N1433">
-        <v>3.16</v>
       </c>
       <c r="O1433">
         <v>1</v>
@@ -73481,13 +73481,13 @@
     </row>
     <row r="1434" spans="1:16">
       <c r="A1434" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1434" t="s">
         <v>235</v>
       </c>
       <c r="C1434">
-        <v>0.1805142502084802</v>
+        <v>0.17539774678287</v>
       </c>
       <c r="D1434" t="s">
         <v>348</v>
@@ -73499,22 +73499,22 @@
         <v>-1</v>
       </c>
       <c r="G1434">
-        <v>0.006699485749791519</v>
+        <v>0.00666460225321713</v>
       </c>
       <c r="H1434">
         <v>0.00640460225321713</v>
       </c>
       <c r="I1434">
-        <v>0.26511650342561</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1434">
         <v>1.48834965743905</v>
       </c>
       <c r="K1434">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="L1434">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="M1434">
         <v>2.18</v>
@@ -73531,46 +73531,46 @@
     </row>
     <row r="1435" spans="1:16">
       <c r="A1435" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1435" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1435">
-        <v>-0.2666896675768924</v>
+        <v>0.1805142502084802</v>
       </c>
       <c r="D1435" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1435">
-        <v>-0.09227218470493925</v>
+        <v>-0.08460225321712977</v>
       </c>
       <c r="F1435">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1435">
-        <v>0.006966689667576892</v>
+        <v>0.006699485749791519</v>
       </c>
       <c r="H1435">
-        <v>0.00699227218470494</v>
+        <v>0.00640460225321713</v>
       </c>
       <c r="I1435">
-        <v>0.1744174828719531</v>
+        <v>0.26511650342561</v>
       </c>
       <c r="J1435">
         <v>1.48834965743905</v>
       </c>
       <c r="K1435">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="L1435">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M1435">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1435">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1435">
         <v>1</v>
@@ -73581,63 +73581,63 @@
     </row>
     <row r="1436" spans="1:16">
       <c r="A1436" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1436" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1436">
-        <v>0.3249624494021601</v>
+        <v>-0.2666896675768924</v>
       </c>
       <c r="D1436" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1436">
-        <v>0.05097181795809602</v>
+        <v>-0.3229615579573877</v>
       </c>
       <c r="F1436">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1436">
-        <v>0.00635503755059784</v>
+        <v>0.006966689667576892</v>
       </c>
       <c r="H1436">
-        <v>0.006849028182041904</v>
+        <v>0.007862961557957387</v>
       </c>
       <c r="I1436">
-        <v>0.2739906314440641</v>
+        <v>-0.05627189038049529</v>
       </c>
       <c r="J1436">
-        <v>1.422187523866906</v>
+        <v>1.48834965743905</v>
       </c>
       <c r="K1436">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1436">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1436">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1436">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1436">
         <v>1</v>
       </c>
       <c r="P1436" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="1437" spans="1:16">
       <c r="A1437" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1437" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C1437">
-        <v>0.3094155684354338</v>
+        <v>0.3249624494021601</v>
       </c>
       <c r="D1437" t="s">
         <v>346</v>
@@ -73649,22 +73649,22 @@
         <v>-1</v>
       </c>
       <c r="G1437">
-        <v>0.007050584431564567</v>
+        <v>0.00635503755059784</v>
       </c>
       <c r="H1437">
         <v>0.006849028182041904</v>
       </c>
       <c r="I1437">
-        <v>0.2584437504773378</v>
+        <v>0.2739906314440641</v>
       </c>
       <c r="J1437">
         <v>1.422187523866906</v>
       </c>
       <c r="K1437">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="L1437">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="M1437">
         <v>2.39</v>
@@ -73681,46 +73681,46 @@
     </row>
     <row r="1438" spans="1:16">
       <c r="A1438" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1438" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C1438">
-        <v>-0.07435943347391838</v>
+        <v>0.3094155684354338</v>
       </c>
       <c r="D1438" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1438">
-        <v>0.2342999465381315</v>
+        <v>0.05097181795809602</v>
       </c>
       <c r="F1438">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1438">
-        <v>0.006894359433473919</v>
+        <v>0.007050584431564567</v>
       </c>
       <c r="H1438">
-        <v>0.006605700053461869</v>
+        <v>0.006849028182041904</v>
       </c>
       <c r="I1438">
-        <v>0.3086593800120498</v>
+        <v>0.2584437504773378</v>
       </c>
       <c r="J1438">
         <v>1.422187523866906</v>
       </c>
       <c r="K1438">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="L1438">
-        <v>3.41</v>
+        <v>3.68</v>
       </c>
       <c r="M1438">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1438">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1438">
         <v>1</v>
@@ -73731,13 +73731,13 @@
     </row>
     <row r="1439" spans="1:16">
       <c r="A1439" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1439" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C1439">
-        <v>-0.1028031839512566</v>
+        <v>-0.1128031839512569</v>
       </c>
       <c r="D1439" t="s">
         <v>347</v>
@@ -73749,13 +73749,13 @@
         <v>1</v>
       </c>
       <c r="G1439">
-        <v>0.006922803183951257</v>
+        <v>0.006912803183951256</v>
       </c>
       <c r="H1439">
         <v>0.006605700053461869</v>
       </c>
       <c r="I1439">
-        <v>0.3371031304893881</v>
+        <v>0.3471031304893883</v>
       </c>
       <c r="J1439">
         <v>1.422187523866906</v>
@@ -73764,7 +73764,7 @@
         <v>2.47</v>
       </c>
       <c r="L1439">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="M1439">
         <v>2.24</v>
@@ -73781,46 +73781,46 @@
     </row>
     <row r="1440" spans="1:16">
       <c r="A1440" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1440" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1440">
-        <v>0.3196311979701458</v>
+        <v>-0.1028031839512566</v>
       </c>
       <c r="D1440" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1440">
-        <v>0.05963119797014604</v>
+        <v>0.2342999465381315</v>
       </c>
       <c r="F1440">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1440">
-        <v>0.006520368802029853</v>
+        <v>0.006922803183951257</v>
       </c>
       <c r="H1440">
-        <v>0.006260368802029854</v>
+        <v>0.006605700053461869</v>
       </c>
       <c r="I1440">
-        <v>0.2599999999999998</v>
+        <v>0.3371031304893881</v>
       </c>
       <c r="J1440">
         <v>1.422187523866906</v>
       </c>
       <c r="K1440">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1440">
+        <v>3.41</v>
+      </c>
+      <c r="M1440">
+        <v>2.24</v>
+      </c>
+      <c r="N1440">
         <v>3.42</v>
-      </c>
-      <c r="M1440">
-        <v>2.18</v>
-      </c>
-      <c r="N1440">
-        <v>3.16</v>
       </c>
       <c r="O1440">
         <v>1</v>
@@ -73831,13 +73831,13 @@
     </row>
     <row r="1441" spans="1:16">
       <c r="A1441" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1441" t="s">
         <v>235</v>
       </c>
       <c r="C1441">
-        <v>0.3254093227314772</v>
+        <v>0.3196311979701458</v>
       </c>
       <c r="D1441" t="s">
         <v>348</v>
@@ -73849,22 +73849,22 @@
         <v>-1</v>
       </c>
       <c r="G1441">
-        <v>0.006554590677268523</v>
+        <v>0.006520368802029853</v>
       </c>
       <c r="H1441">
         <v>0.006260368802029854</v>
       </c>
       <c r="I1441">
-        <v>0.2657781247613311</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1441">
         <v>1.422187523866906</v>
       </c>
       <c r="K1441">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="L1441">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="M1441">
         <v>2.18</v>
@@ -73881,46 +73881,46 @@
     </row>
     <row r="1442" spans="1:16">
       <c r="A1442" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1442" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1442">
-        <v>-0.1059156829965806</v>
+        <v>0.3254093227314772</v>
       </c>
       <c r="D1442" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1442">
-        <v>0.06519369319676516</v>
+        <v>0.05963119797014604</v>
       </c>
       <c r="F1442">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1442">
-        <v>0.006805915682996581</v>
+        <v>0.006554590677268523</v>
       </c>
       <c r="H1442">
-        <v>0.006834806306803236</v>
+        <v>0.006260368802029854</v>
       </c>
       <c r="I1442">
-        <v>0.1711093761933458</v>
+        <v>0.2657781247613311</v>
       </c>
       <c r="J1442">
         <v>1.422187523866906</v>
       </c>
       <c r="K1442">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="L1442">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M1442">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1442">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1442">
         <v>1</v>
@@ -73931,63 +73931,63 @@
     </row>
     <row r="1443" spans="1:16">
       <c r="A1443" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1443" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1443">
-        <v>0.4152357957730102</v>
+        <v>-0.1059156829965806</v>
       </c>
       <c r="D1443" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1443">
-        <v>0.1527422414610826</v>
+        <v>-0.1410156906339899</v>
       </c>
       <c r="F1443">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1443">
-        <v>0.006264764204226989</v>
+        <v>0.006805915682996581</v>
       </c>
       <c r="H1443">
-        <v>0.006747257758538919</v>
+        <v>0.007681015690633989</v>
       </c>
       <c r="I1443">
-        <v>0.2624935543119276</v>
+        <v>-0.03510000763740928</v>
       </c>
       <c r="J1443">
-        <v>1.379605756710844</v>
+        <v>1.422187523866906</v>
       </c>
       <c r="K1443">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1443">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1443">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1443">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1443">
         <v>1</v>
       </c>
       <c r="P1443" t="s">
-        <v>345</v>
+        <v>481</v>
       </c>
     </row>
     <row r="1444" spans="1:16">
       <c r="A1444" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1444" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C1444">
-        <v>0.4103343565952993</v>
+        <v>0.4152357957730102</v>
       </c>
       <c r="D1444" t="s">
         <v>346</v>
@@ -73999,22 +73999,22 @@
         <v>-1</v>
       </c>
       <c r="G1444">
-        <v>0.006949665643404702</v>
+        <v>0.006264764204226989</v>
       </c>
       <c r="H1444">
         <v>0.006747257758538919</v>
       </c>
       <c r="I1444">
-        <v>0.2575921151342166</v>
+        <v>0.2624935543119276</v>
       </c>
       <c r="J1444">
         <v>1.379605756710844</v>
       </c>
       <c r="K1444">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="L1444">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="M1444">
         <v>2.39</v>
@@ -74031,46 +74031,46 @@
     </row>
     <row r="1445" spans="1:16">
       <c r="A1445" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1445" t="s">
         <v>237</v>
       </c>
       <c r="C1445">
-        <v>-0.007626219075785645</v>
+        <v>0.4103343565952993</v>
       </c>
       <c r="D1445" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1445">
-        <v>0.3296831049677085</v>
+        <v>0.1527422414610826</v>
       </c>
       <c r="F1445">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1445">
-        <v>0.006807626219075786</v>
+        <v>0.006949665643404702</v>
       </c>
       <c r="H1445">
-        <v>0.006510316895032292</v>
+        <v>0.006747257758538919</v>
       </c>
       <c r="I1445">
-        <v>0.3373093240434941</v>
+        <v>0.2575921151342166</v>
       </c>
       <c r="J1445">
         <v>1.379605756710844</v>
       </c>
       <c r="K1445">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="L1445">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="M1445">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1445">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1445">
         <v>1</v>
@@ -74081,13 +74081,13 @@
     </row>
     <row r="1446" spans="1:16">
       <c r="A1446" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1446" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C1446">
-        <v>0.002373780924214586</v>
+        <v>-0.007626219075785645</v>
       </c>
       <c r="D1446" t="s">
         <v>347</v>
@@ -74099,13 +74099,13 @@
         <v>1</v>
       </c>
       <c r="G1446">
-        <v>0.006817626219075786</v>
+        <v>0.006807626219075786</v>
       </c>
       <c r="H1446">
         <v>0.006510316895032292</v>
       </c>
       <c r="I1446">
-        <v>0.3273093240434939</v>
+        <v>0.3373093240434941</v>
       </c>
       <c r="J1446">
         <v>1.379605756710844</v>
@@ -74114,7 +74114,7 @@
         <v>2.47</v>
       </c>
       <c r="L1446">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="M1446">
         <v>2.24</v>
@@ -74131,46 +74131,46 @@
     </row>
     <row r="1447" spans="1:16">
       <c r="A1447" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1447" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C1447">
-        <v>0.4124594503703594</v>
+        <v>0.002373780924214586</v>
       </c>
       <c r="D1447" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1447">
-        <v>0.1524594503703596</v>
+        <v>0.3296831049677085</v>
       </c>
       <c r="F1447">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1447">
-        <v>0.00642754054962964</v>
+        <v>0.006817626219075786</v>
       </c>
       <c r="H1447">
-        <v>0.00616754054962964</v>
+        <v>0.006510316895032292</v>
       </c>
       <c r="I1447">
-        <v>0.2599999999999998</v>
+        <v>0.3273093240434939</v>
       </c>
       <c r="J1447">
         <v>1.379605756710844</v>
       </c>
       <c r="K1447">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1447">
+        <v>3.41</v>
+      </c>
+      <c r="M1447">
+        <v>2.24</v>
+      </c>
+      <c r="N1447">
         <v>3.42</v>
-      </c>
-      <c r="M1447">
-        <v>2.18</v>
-      </c>
-      <c r="N1447">
-        <v>3.16</v>
       </c>
       <c r="O1447">
         <v>1</v>
@@ -74181,13 +74181,13 @@
     </row>
     <row r="1448" spans="1:16">
       <c r="A1448" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1448" t="s">
         <v>235</v>
       </c>
       <c r="C1448">
-        <v>0.4186633928032513</v>
+        <v>0.4124594503703594</v>
       </c>
       <c r="D1448" t="s">
         <v>348</v>
@@ -74199,22 +74199,22 @@
         <v>-1</v>
       </c>
       <c r="G1448">
-        <v>0.006461336607196749</v>
+        <v>0.00642754054962964</v>
       </c>
       <c r="H1448">
         <v>0.00616754054962964</v>
       </c>
       <c r="I1448">
-        <v>0.2662039424328917</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1448">
         <v>1.379605756710844</v>
       </c>
       <c r="K1448">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="L1448">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="M1448">
         <v>2.18</v>
@@ -74231,46 +74231,46 @@
     </row>
     <row r="1449" spans="1:16">
       <c r="A1449" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1449" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C1449">
-        <v>-0.002441988807351692</v>
+        <v>0.4186633928032513</v>
       </c>
       <c r="D1449" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E1449">
-        <v>0.1665382990281912</v>
+        <v>0.1524594503703596</v>
       </c>
       <c r="F1449">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1449">
-        <v>0.006702441988807352</v>
+        <v>0.006461336607196749</v>
       </c>
       <c r="H1449">
-        <v>0.006733461700971809</v>
+        <v>0.00616754054962964</v>
       </c>
       <c r="I1449">
-        <v>0.1689802878355429</v>
+        <v>0.2662039424328917</v>
       </c>
       <c r="J1449">
         <v>1.379605756710844</v>
       </c>
       <c r="K1449">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="L1449">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M1449">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="N1449">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1449">
         <v>1</v>
@@ -74281,63 +74281,63 @@
     </row>
     <row r="1450" spans="1:16">
       <c r="A1450" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1450" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C1450">
-        <v>0.4887758368955271</v>
+        <v>-0.002441988807351692</v>
       </c>
       <c r="D1450" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E1450">
-        <v>0.2356482312171275</v>
+        <v>-0.02391583095482153</v>
       </c>
       <c r="F1450">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1450">
-        <v>0.006191224163104472</v>
+        <v>0.006702441988807352</v>
       </c>
       <c r="H1450">
-        <v>0.006664351768782873</v>
+        <v>0.007563915830954821</v>
       </c>
       <c r="I1450">
-        <v>0.2531276056783995</v>
+        <v>-0.02147384214746983</v>
       </c>
       <c r="J1450">
-        <v>1.344917058068148</v>
+        <v>1.379605756710844</v>
       </c>
       <c r="K1450">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1450">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1450">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="N1450">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1450">
         <v>1</v>
       </c>
       <c r="P1450" t="s">
-        <v>482</v>
+        <v>345</v>
       </c>
     </row>
     <row r="1451" spans="1:16">
       <c r="A1451" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1451" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C1451">
-        <v>0.4925465723784903</v>
+        <v>0.4887758368955271</v>
       </c>
       <c r="D1451" t="s">
         <v>346</v>
@@ -74349,22 +74349,22 @@
         <v>-1</v>
       </c>
       <c r="G1451">
-        <v>0.00686745342762151</v>
+        <v>0.006191224163104472</v>
       </c>
       <c r="H1451">
         <v>0.006664351768782873</v>
       </c>
       <c r="I1451">
-        <v>0.2568983411613628</v>
+        <v>0.2531276056783995</v>
       </c>
       <c r="J1451">
         <v>1.344917058068148</v>
       </c>
       <c r="K1451">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="L1451">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="M1451">
         <v>2.39</v>
@@ -74381,10 +74381,10 @@
     </row>
     <row r="1452" spans="1:16">
       <c r="A1452" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1452" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1452">
         <v>0.07805486657167515</v>
@@ -74431,7 +74431,7 @@
     </row>
     <row r="1453" spans="1:16">
       <c r="A1453" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1453" t="s">
         <v>232</v>
@@ -74481,10 +74481,10 @@
     </row>
     <row r="1454" spans="1:16">
       <c r="A1454" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1454" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1454">
         <v>0.4880808134114383</v>
@@ -74531,10 +74531,10 @@
     </row>
     <row r="1455" spans="1:16">
       <c r="A1455" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1455" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C1455">
         <v>0.4946316428307571</v>
@@ -74581,7 +74581,7 @@
     </row>
     <row r="1456" spans="1:16">
       <c r="A1456" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1456" t="s">
         <v>226</v>
@@ -74590,10 +74590,10 @@
         <v>0.08185154889440138</v>
       </c>
       <c r="D1456" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E1456">
-        <v>0.2490974017978091</v>
+        <v>0.07147809031259422</v>
       </c>
       <c r="F1456">
         <v>1</v>
@@ -74602,10 +74602,10 @@
         <v>0.006618148451105599</v>
       </c>
       <c r="H1456">
-        <v>0.006650902598202191</v>
+        <v>0.007468521909687406</v>
       </c>
       <c r="I1456">
-        <v>0.1672458529034078</v>
+        <v>-0.01037345858180716</v>
       </c>
       <c r="J1456">
         <v>1.344917058068148</v>
@@ -74617,10 +74617,10 @@
         <v>3.35</v>
       </c>
       <c r="M1456">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="N1456">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1456">
         <v>1</v>
@@ -74684,7 +74684,7 @@
         <v>1</v>
       </c>
       <c r="B1458" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1458">
         <v>0.1258739649902756</v>
@@ -74784,7 +74784,7 @@
         <v>3</v>
       </c>
       <c r="B1460" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1460">
         <v>0.5302855237565995</v>
@@ -74834,7 +74834,7 @@
         <v>4</v>
       </c>
       <c r="B1461" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C1461">
         <v>0.5370299527646578</v>
@@ -74890,10 +74890,10 @@
         <v>0.1288962489580445</v>
       </c>
       <c r="D1462" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E1462">
-        <v>0.295174103917756</v>
+        <v>0.1247179772158944</v>
       </c>
       <c r="F1462">
         <v>1</v>
@@ -74902,10 +74902,10 @@
         <v>0.006571103751041956</v>
       </c>
       <c r="H1462">
-        <v>0.006604825896082245</v>
+        <v>0.007415282022784106</v>
       </c>
       <c r="I1462">
-        <v>0.1662778549597115</v>
+        <v>-0.00417827174215013</v>
       </c>
       <c r="J1462">
         <v>1.32555709919422</v>
@@ -74917,10 +74917,10 @@
         <v>3.35</v>
       </c>
       <c r="M1462">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="N1462">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1462">
         <v>1</v>
@@ -74984,7 +74984,7 @@
         <v>1</v>
       </c>
       <c r="B1464" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1464">
         <v>0.1156504395889431</v>
@@ -75084,7 +75084,7 @@
         <v>3</v>
       </c>
       <c r="B1466" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1466">
         <v>0.5212623312971241</v>
@@ -75134,7 +75134,7 @@
         <v>4</v>
       </c>
       <c r="B1467" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C1467">
         <v>0.5279653695140833</v>
@@ -75190,10 +75190,10 @@
         <v>0.1188382867211062</v>
       </c>
       <c r="D1468" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E1468">
-        <v>0.28532309563631</v>
+        <v>0.1133355096638033</v>
       </c>
       <c r="F1468">
         <v>1</v>
@@ -75202,10 +75202,10 @@
         <v>0.006581161713278894</v>
       </c>
       <c r="H1468">
-        <v>0.006614676904363691</v>
+        <v>0.007426664490336197</v>
       </c>
       <c r="I1468">
-        <v>0.1664848089152038</v>
+        <v>-0.005502777057302843</v>
       </c>
       <c r="J1468">
         <v>1.329696178304071</v>
@@ -75217,10 +75217,10 @@
         <v>3.35</v>
       </c>
       <c r="M1468">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="N1468">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1468">
         <v>1</v>
@@ -75284,7 +75284,7 @@
         <v>1</v>
       </c>
       <c r="B1470" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1470">
         <v>0.1695571540866143</v>
@@ -75384,7 +75384,7 @@
         <v>3</v>
       </c>
       <c r="B1472" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1472">
         <v>0.5688399173719918</v>
@@ -75434,7 +75434,7 @@
         <v>4</v>
       </c>
       <c r="B1473" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C1473">
         <v>0.575761201396634</v>
@@ -75490,10 +75490,10 @@
         <v>0.1718720179880457</v>
       </c>
       <c r="D1474" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E1474">
-        <v>0.3372655978648353</v>
+        <v>0.1733531067765952</v>
       </c>
       <c r="F1474">
         <v>1</v>
@@ -75502,10 +75502,10 @@
         <v>0.006528127982011954</v>
       </c>
       <c r="H1474">
-        <v>0.006562734402135165</v>
+        <v>0.007366646893223405</v>
       </c>
       <c r="I1474">
-        <v>0.1653935798767896</v>
+        <v>0.001481088788549467</v>
       </c>
       <c r="J1474">
         <v>1.307871597535784</v>
@@ -75517,10 +75517,10 @@
         <v>3.35</v>
       </c>
       <c r="M1474">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="N1474">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1474">
         <v>1</v>
@@ -75584,7 +75584,7 @@
         <v>1</v>
       </c>
       <c r="B1476" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C1476">
         <v>0.2864345279925038</v>
@@ -75684,7 +75684,7 @@
         <v>3</v>
       </c>
       <c r="B1478" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C1478">
         <v>0.6719948465682828</v>
@@ -75734,7 +75734,7 @@
         <v>4</v>
       </c>
       <c r="B1479" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C1479">
         <v>0.6793893183415323</v>
@@ -75790,10 +75790,10 @@
         <v>0.2868566408995079</v>
       </c>
       <c r="D1480" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E1480">
-        <v>0.4498842820332634</v>
+        <v>0.3034797376434764</v>
       </c>
       <c r="F1480">
         <v>1</v>
@@ -75802,10 +75802,10 @@
         <v>0.006413143359100492</v>
       </c>
       <c r="H1480">
-        <v>0.006450115717966737</v>
+        <v>0.007236520262356523</v>
       </c>
       <c r="I1480">
-        <v>0.1630276411337555</v>
+        <v>0.01662309674396845</v>
       </c>
       <c r="J1480">
         <v>1.260552822675099</v>
@@ -75817,10 +75817,10 @@
         <v>3.35</v>
       </c>
       <c r="M1480">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="N1480">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O1480">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4431" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4449" uniqueCount="479">
   <si>
     <t>trade_time</t>
   </si>
@@ -1069,7 +1069,7 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2016-04-22</t>
@@ -1808,7 +1808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1473"/>
+  <dimension ref="A1:P1479"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -73113,43 +73113,43 @@
         <v>1</v>
       </c>
       <c r="B1427" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C1427">
-        <v>-0.007626219075785645</v>
+        <v>0.4103343565952993</v>
       </c>
       <c r="D1427" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E1427">
-        <v>0.3296831049677085</v>
+        <v>0.1527422414610826</v>
       </c>
       <c r="F1427">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1427">
-        <v>0.006807626219075786</v>
+        <v>0.006949665643404702</v>
       </c>
       <c r="H1427">
-        <v>0.006510316895032292</v>
+        <v>0.006747257758538919</v>
       </c>
       <c r="I1427">
-        <v>0.3373093240434941</v>
+        <v>0.2575921151342166</v>
       </c>
       <c r="J1427">
         <v>1.379605756710844</v>
       </c>
       <c r="K1427">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="L1427">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="M1427">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1427">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1427">
         <v>1</v>
@@ -73163,10 +73163,10 @@
         <v>2</v>
       </c>
       <c r="B1428" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1428">
-        <v>0.002373780924214586</v>
+        <v>-0.007626219075785645</v>
       </c>
       <c r="D1428" t="s">
         <v>340</v>
@@ -73178,13 +73178,13 @@
         <v>1</v>
       </c>
       <c r="G1428">
-        <v>0.006817626219075786</v>
+        <v>0.006807626219075786</v>
       </c>
       <c r="H1428">
         <v>0.006510316895032292</v>
       </c>
       <c r="I1428">
-        <v>0.3273093240434939</v>
+        <v>0.3373093240434941</v>
       </c>
       <c r="J1428">
         <v>1.379605756710844</v>
@@ -73193,7 +73193,7 @@
         <v>2.47</v>
       </c>
       <c r="L1428">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="M1428">
         <v>2.24</v>
@@ -73213,43 +73213,43 @@
         <v>3</v>
       </c>
       <c r="B1429" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C1429">
-        <v>0.4124594503703594</v>
+        <v>0.002373780924214586</v>
       </c>
       <c r="D1429" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E1429">
-        <v>0.1524594503703596</v>
+        <v>0.3296831049677085</v>
       </c>
       <c r="F1429">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1429">
-        <v>0.00642754054962964</v>
+        <v>0.006817626219075786</v>
       </c>
       <c r="H1429">
-        <v>0.00616754054962964</v>
+        <v>0.006510316895032292</v>
       </c>
       <c r="I1429">
-        <v>0.2599999999999998</v>
+        <v>0.3273093240434939</v>
       </c>
       <c r="J1429">
         <v>1.379605756710844</v>
       </c>
       <c r="K1429">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1429">
+        <v>3.41</v>
+      </c>
+      <c r="M1429">
+        <v>2.24</v>
+      </c>
+      <c r="N1429">
         <v>3.42</v>
-      </c>
-      <c r="M1429">
-        <v>2.18</v>
-      </c>
-      <c r="N1429">
-        <v>3.16</v>
       </c>
       <c r="O1429">
         <v>1</v>
@@ -73263,43 +73263,43 @@
         <v>4</v>
       </c>
       <c r="B1430" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C1430">
-        <v>-0.002441988807351692</v>
+        <v>0.4124594503703594</v>
       </c>
       <c r="D1430" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1430">
-        <v>0.2278408022833713</v>
+        <v>0.1524594503703596</v>
       </c>
       <c r="F1430">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1430">
-        <v>0.006702441988807352</v>
+        <v>0.00642754054962964</v>
       </c>
       <c r="H1430">
-        <v>0.00751215919771663</v>
+        <v>0.00616754054962964</v>
       </c>
       <c r="I1430">
-        <v>0.230282791090723</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1430">
         <v>1.379605756710844</v>
       </c>
       <c r="K1430">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="L1430">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="M1430">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1430">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1430">
         <v>1</v>
@@ -73313,43 +73313,43 @@
         <v>5</v>
       </c>
       <c r="B1431" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C1431">
-        <v>-0.02391583095482153</v>
+        <v>0.4186633928032513</v>
       </c>
       <c r="D1431" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1431">
-        <v>0.2278408022833713</v>
+        <v>0.1524594503703596</v>
       </c>
       <c r="F1431">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1431">
-        <v>0.007563915830954821</v>
+        <v>0.006461336607196749</v>
       </c>
       <c r="H1431">
-        <v>0.00751215919771663</v>
+        <v>0.00616754054962964</v>
       </c>
       <c r="I1431">
-        <v>0.2517566332381929</v>
+        <v>0.2662039424328917</v>
       </c>
       <c r="J1431">
         <v>1.379605756710844</v>
       </c>
       <c r="K1431">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="L1431">
-        <v>3.77</v>
+        <v>3.44</v>
       </c>
       <c r="M1431">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1431">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1431">
         <v>1</v>
@@ -73363,10 +73363,10 @@
         <v>6</v>
       </c>
       <c r="B1432" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C1432">
-        <v>-0.0491000612232555</v>
+        <v>-0.002441988807351692</v>
       </c>
       <c r="D1432" t="s">
         <v>347</v>
@@ -73378,22 +73378,22 @@
         <v>1</v>
       </c>
       <c r="G1432">
-        <v>0.007649100061223255</v>
+        <v>0.006702441988807352</v>
       </c>
       <c r="H1432">
         <v>0.00751215919771663</v>
       </c>
       <c r="I1432">
-        <v>0.2769408635066268</v>
+        <v>0.230282791090723</v>
       </c>
       <c r="J1432">
         <v>1.379605756710844</v>
       </c>
       <c r="K1432">
-        <v>2.79</v>
+        <v>2.43</v>
       </c>
       <c r="L1432">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="M1432">
         <v>2.64</v>
@@ -73413,10 +73413,10 @@
         <v>7</v>
       </c>
       <c r="B1433" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1433">
-        <v>0.004695996343853093</v>
+        <v>-0.02391583095482153</v>
       </c>
       <c r="D1433" t="s">
         <v>347</v>
@@ -73428,22 +73428,22 @@
         <v>1</v>
       </c>
       <c r="G1433">
-        <v>0.007675304003656147</v>
+        <v>0.007563915830954821</v>
       </c>
       <c r="H1433">
         <v>0.00751215919771663</v>
       </c>
       <c r="I1433">
-        <v>0.2231448059395182</v>
+        <v>0.2517566332381929</v>
       </c>
       <c r="J1433">
         <v>1.379605756710844</v>
       </c>
       <c r="K1433">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="L1433">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="M1433">
         <v>2.64</v>
@@ -73460,146 +73460,146 @@
     </row>
     <row r="1434" spans="1:16">
       <c r="A1434" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1434" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C1434">
-        <v>0.4887758368955271</v>
+        <v>-0.0491000612232555</v>
       </c>
       <c r="D1434" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E1434">
-        <v>0.2356482312171275</v>
+        <v>0.2278408022833713</v>
       </c>
       <c r="F1434">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1434">
-        <v>0.006191224163104472</v>
+        <v>0.007649100061223255</v>
       </c>
       <c r="H1434">
-        <v>0.006664351768782873</v>
+        <v>0.00751215919771663</v>
       </c>
       <c r="I1434">
-        <v>0.2531276056783995</v>
+        <v>0.2769408635066268</v>
       </c>
       <c r="J1434">
-        <v>1.344917058068148</v>
+        <v>1.379605756710844</v>
       </c>
       <c r="K1434">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="L1434">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="M1434">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="N1434">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="O1434">
         <v>1</v>
       </c>
       <c r="P1434" t="s">
-        <v>475</v>
+        <v>338</v>
       </c>
     </row>
     <row r="1435" spans="1:16">
       <c r="A1435" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1435" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C1435">
-        <v>0.07805486657167515</v>
+        <v>0.004695996343853093</v>
       </c>
       <c r="D1435" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1435">
-        <v>0.407385789927349</v>
+        <v>0.2278408022833713</v>
       </c>
       <c r="F1435">
         <v>1</v>
       </c>
       <c r="G1435">
-        <v>0.006721945133428324</v>
+        <v>0.007675304003656147</v>
       </c>
       <c r="H1435">
-        <v>0.006432614210072651</v>
+        <v>0.00751215919771663</v>
       </c>
       <c r="I1435">
-        <v>0.3293309233556738</v>
+        <v>0.2231448059395182</v>
       </c>
       <c r="J1435">
-        <v>1.344917058068148</v>
+        <v>1.379605756710844</v>
       </c>
       <c r="K1435">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="L1435">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="M1435">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1435">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1435">
         <v>1</v>
       </c>
       <c r="P1435" t="s">
-        <v>475</v>
+        <v>338</v>
       </c>
     </row>
     <row r="1436" spans="1:16">
       <c r="A1436" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1436" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1436">
-        <v>0.08805486657167538</v>
+        <v>0.4887758368955271</v>
       </c>
       <c r="D1436" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E1436">
-        <v>0.407385789927349</v>
+        <v>0.2356482312171275</v>
       </c>
       <c r="F1436">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1436">
-        <v>0.006731945133428325</v>
+        <v>0.006191224163104472</v>
       </c>
       <c r="H1436">
-        <v>0.006432614210072651</v>
+        <v>0.006664351768782873</v>
       </c>
       <c r="I1436">
-        <v>0.3193309233556736</v>
+        <v>0.2531276056783995</v>
       </c>
       <c r="J1436">
         <v>1.344917058068148</v>
       </c>
       <c r="K1436">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="L1436">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="M1436">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="N1436">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="O1436">
         <v>1</v>
@@ -73610,46 +73610,46 @@
     </row>
     <row r="1437" spans="1:16">
       <c r="A1437" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1437" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1437">
-        <v>0.4880808134114383</v>
+        <v>0.07805486657167515</v>
       </c>
       <c r="D1437" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E1437">
-        <v>0.2280808134114385</v>
+        <v>0.407385789927349</v>
       </c>
       <c r="F1437">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1437">
-        <v>0.006351919186588562</v>
+        <v>0.006721945133428324</v>
       </c>
       <c r="H1437">
-        <v>0.006091919186588563</v>
+        <v>0.006432614210072651</v>
       </c>
       <c r="I1437">
-        <v>0.2599999999999998</v>
+        <v>0.3293309233556738</v>
       </c>
       <c r="J1437">
         <v>1.344917058068148</v>
       </c>
       <c r="K1437">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L1437">
+        <v>3.4</v>
+      </c>
+      <c r="M1437">
+        <v>2.24</v>
+      </c>
+      <c r="N1437">
         <v>3.42</v>
-      </c>
-      <c r="M1437">
-        <v>2.18</v>
-      </c>
-      <c r="N1437">
-        <v>3.16</v>
       </c>
       <c r="O1437">
         <v>1</v>
@@ -73660,46 +73660,46 @@
     </row>
     <row r="1438" spans="1:16">
       <c r="A1438" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1438" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C1438">
-        <v>0.08185154889440138</v>
+        <v>0.08805486657167538</v>
       </c>
       <c r="D1438" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1438">
-        <v>0.3194189667000904</v>
+        <v>0.407385789927349</v>
       </c>
       <c r="F1438">
         <v>1</v>
       </c>
       <c r="G1438">
-        <v>0.006618148451105599</v>
+        <v>0.006731945133428325</v>
       </c>
       <c r="H1438">
-        <v>0.00742058103329991</v>
+        <v>0.006432614210072651</v>
       </c>
       <c r="I1438">
-        <v>0.237567417805689</v>
+        <v>0.3193309233556736</v>
       </c>
       <c r="J1438">
         <v>1.344917058068148</v>
       </c>
       <c r="K1438">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="L1438">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="M1438">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1438">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1438">
         <v>1</v>
@@ -73710,46 +73710,46 @@
     </row>
     <row r="1439" spans="1:16">
       <c r="A1439" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1439" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C1439">
-        <v>0.07147809031259422</v>
+        <v>0.4880808134114383</v>
       </c>
       <c r="D1439" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1439">
-        <v>0.3194189667000904</v>
+        <v>0.2280808134114385</v>
       </c>
       <c r="F1439">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1439">
-        <v>0.007468521909687406</v>
+        <v>0.006351919186588562</v>
       </c>
       <c r="H1439">
-        <v>0.00742058103329991</v>
+        <v>0.006091919186588563</v>
       </c>
       <c r="I1439">
-        <v>0.2479408763874962</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1439">
         <v>1.344917058068148</v>
       </c>
       <c r="K1439">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="L1439">
-        <v>3.77</v>
+        <v>3.42</v>
       </c>
       <c r="M1439">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1439">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1439">
         <v>1</v>
@@ -73760,46 +73760,46 @@
     </row>
     <row r="1440" spans="1:16">
       <c r="A1440" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1440" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C1440">
-        <v>0.04768140798986797</v>
+        <v>0.4946316428307571</v>
       </c>
       <c r="D1440" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1440">
-        <v>0.3194189667000904</v>
+        <v>0.2280808134114385</v>
       </c>
       <c r="F1440">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1440">
-        <v>0.007552318592010132</v>
+        <v>0.006385368357169244</v>
       </c>
       <c r="H1440">
-        <v>0.00742058103329991</v>
+        <v>0.006091919186588563</v>
       </c>
       <c r="I1440">
-        <v>0.2717375587102224</v>
+        <v>0.2665508294193186</v>
       </c>
       <c r="J1440">
         <v>1.344917058068148</v>
       </c>
       <c r="K1440">
-        <v>2.79</v>
+        <v>2.19</v>
       </c>
       <c r="L1440">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="M1440">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1440">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1440">
         <v>1</v>
@@ -73810,13 +73810,13 @@
     </row>
     <row r="1441" spans="1:16">
       <c r="A1441" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1441" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C1441">
-        <v>0.1011305785705501</v>
+        <v>0.08185154889440138</v>
       </c>
       <c r="D1441" t="s">
         <v>347</v>
@@ -73828,22 +73828,22 @@
         <v>1</v>
       </c>
       <c r="G1441">
-        <v>0.00757886942142945</v>
+        <v>0.006618148451105599</v>
       </c>
       <c r="H1441">
         <v>0.00742058103329991</v>
       </c>
       <c r="I1441">
-        <v>0.2182883881295403</v>
+        <v>0.237567417805689</v>
       </c>
       <c r="J1441">
         <v>1.344917058068148</v>
       </c>
       <c r="K1441">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="L1441">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="M1441">
         <v>2.64</v>
@@ -73860,196 +73860,196 @@
     </row>
     <row r="1442" spans="1:16">
       <c r="A1442" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1442" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C1442">
-        <v>0.5298189497082526</v>
+        <v>0.07147809031259422</v>
       </c>
       <c r="D1442" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E1442">
-        <v>0.2819185329258134</v>
+        <v>0.3194189667000904</v>
       </c>
       <c r="F1442">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1442">
-        <v>0.006150181050291748</v>
+        <v>0.007468521909687406</v>
       </c>
       <c r="H1442">
-        <v>0.006618081467074188</v>
+        <v>0.00742058103329991</v>
       </c>
       <c r="I1442">
-        <v>0.2479004167824392</v>
+        <v>0.2479408763874962</v>
       </c>
       <c r="J1442">
-        <v>1.32555709919422</v>
+        <v>1.344917058068148</v>
       </c>
       <c r="K1442">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="L1442">
-        <v>3.34</v>
+        <v>3.77</v>
       </c>
       <c r="M1442">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="N1442">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="O1442">
         <v>1</v>
       </c>
       <c r="P1442" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1443" spans="1:16">
       <c r="A1443" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B1443" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C1443">
-        <v>0.1258739649902756</v>
+        <v>0.04768140798986797</v>
       </c>
       <c r="D1443" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1443">
-        <v>0.4507520978049464</v>
+        <v>0.3194189667000904</v>
       </c>
       <c r="F1443">
         <v>1</v>
       </c>
       <c r="G1443">
-        <v>0.006674126035009724</v>
+        <v>0.007552318592010132</v>
       </c>
       <c r="H1443">
-        <v>0.006389247902195054</v>
+        <v>0.00742058103329991</v>
       </c>
       <c r="I1443">
-        <v>0.3248781328146708</v>
+        <v>0.2717375587102224</v>
       </c>
       <c r="J1443">
-        <v>1.32555709919422</v>
+        <v>1.344917058068148</v>
       </c>
       <c r="K1443">
-        <v>2.47</v>
+        <v>2.79</v>
       </c>
       <c r="L1443">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="M1443">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1443">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1443">
         <v>1</v>
       </c>
       <c r="P1443" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1444" spans="1:16">
       <c r="A1444" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B1444" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C1444">
-        <v>0.1358739649902758</v>
+        <v>0.1011305785705501</v>
       </c>
       <c r="D1444" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1444">
-        <v>0.4507520978049464</v>
+        <v>0.3194189667000904</v>
       </c>
       <c r="F1444">
         <v>1</v>
       </c>
       <c r="G1444">
-        <v>0.006684126035009725</v>
+        <v>0.00757886942142945</v>
       </c>
       <c r="H1444">
-        <v>0.006389247902195054</v>
+        <v>0.00742058103329991</v>
       </c>
       <c r="I1444">
-        <v>0.3148781328146706</v>
+        <v>0.2182883881295403</v>
       </c>
       <c r="J1444">
-        <v>1.32555709919422</v>
+        <v>1.344917058068148</v>
       </c>
       <c r="K1444">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="L1444">
-        <v>3.41</v>
+        <v>3.84</v>
       </c>
       <c r="M1444">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1444">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1444">
         <v>1</v>
       </c>
       <c r="P1444" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1445" spans="1:16">
       <c r="A1445" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1445" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C1445">
-        <v>0.5302855237565995</v>
+        <v>0.5298189497082526</v>
       </c>
       <c r="D1445" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E1445">
-        <v>0.2702855237565998</v>
+        <v>0.2819185329258134</v>
       </c>
       <c r="F1445">
         <v>-1</v>
       </c>
       <c r="G1445">
-        <v>0.0063097144762434</v>
+        <v>0.006150181050291748</v>
       </c>
       <c r="H1445">
-        <v>0.0060497144762434</v>
+        <v>0.006618081467074188</v>
       </c>
       <c r="I1445">
-        <v>0.2599999999999998</v>
+        <v>0.2479004167824392</v>
       </c>
       <c r="J1445">
         <v>1.32555709919422</v>
       </c>
       <c r="K1445">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="L1445">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="M1445">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="N1445">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="O1445">
         <v>1</v>
@@ -74060,46 +74060,46 @@
     </row>
     <row r="1446" spans="1:16">
       <c r="A1446" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1446" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C1446">
-        <v>0.1288962489580445</v>
+        <v>0.1258739649902756</v>
       </c>
       <c r="D1446" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1446">
-        <v>0.3705292581272586</v>
+        <v>0.4507520978049464</v>
       </c>
       <c r="F1446">
         <v>1</v>
       </c>
       <c r="G1446">
-        <v>0.006571103751041956</v>
+        <v>0.006674126035009724</v>
       </c>
       <c r="H1446">
-        <v>0.007369470741872742</v>
+        <v>0.006389247902195054</v>
       </c>
       <c r="I1446">
-        <v>0.241633009169214</v>
+        <v>0.3248781328146708</v>
       </c>
       <c r="J1446">
         <v>1.32555709919422</v>
       </c>
       <c r="K1446">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="L1446">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="M1446">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1446">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1446">
         <v>1</v>
@@ -74110,46 +74110,46 @@
     </row>
     <row r="1447" spans="1:16">
       <c r="A1447" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1447" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C1447">
-        <v>0.1247179772158944</v>
+        <v>0.1358739649902758</v>
       </c>
       <c r="D1447" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1447">
-        <v>0.3705292581272586</v>
+        <v>0.4507520978049464</v>
       </c>
       <c r="F1447">
         <v>1</v>
       </c>
       <c r="G1447">
-        <v>0.007415282022784106</v>
+        <v>0.006684126035009725</v>
       </c>
       <c r="H1447">
-        <v>0.007369470741872742</v>
+        <v>0.006389247902195054</v>
       </c>
       <c r="I1447">
-        <v>0.2458112809113642</v>
+        <v>0.3148781328146706</v>
       </c>
       <c r="J1447">
         <v>1.32555709919422</v>
       </c>
       <c r="K1447">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="L1447">
-        <v>3.77</v>
+        <v>3.41</v>
       </c>
       <c r="M1447">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1447">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1447">
         <v>1</v>
@@ -74160,46 +74160,46 @@
     </row>
     <row r="1448" spans="1:16">
       <c r="A1448" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1448" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C1448">
-        <v>0.1016956932481254</v>
+        <v>0.5302855237565995</v>
       </c>
       <c r="D1448" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1448">
-        <v>0.3705292581272586</v>
+        <v>0.2702855237565998</v>
       </c>
       <c r="F1448">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1448">
-        <v>0.007498304306751875</v>
+        <v>0.0063097144762434</v>
       </c>
       <c r="H1448">
-        <v>0.007369470741872742</v>
+        <v>0.0060497144762434</v>
       </c>
       <c r="I1448">
-        <v>0.2688335648791331</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1448">
         <v>1.32555709919422</v>
       </c>
       <c r="K1448">
-        <v>2.79</v>
+        <v>2.18</v>
       </c>
       <c r="L1448">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="M1448">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1448">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1448">
         <v>1</v>
@@ -74210,46 +74210,46 @@
     </row>
     <row r="1449" spans="1:16">
       <c r="A1449" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1449" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C1449">
-        <v>0.1549512642400677</v>
+        <v>0.5370299527646578</v>
       </c>
       <c r="D1449" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1449">
-        <v>0.3705292581272586</v>
+        <v>0.2702855237565998</v>
       </c>
       <c r="F1449">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1449">
-        <v>0.007525048735759932</v>
+        <v>0.006342970047235342</v>
       </c>
       <c r="H1449">
-        <v>0.007369470741872742</v>
+        <v>0.0060497144762434</v>
       </c>
       <c r="I1449">
-        <v>0.2155779938871909</v>
+        <v>0.2667444290080581</v>
       </c>
       <c r="J1449">
         <v>1.32555709919422</v>
       </c>
       <c r="K1449">
-        <v>2.78</v>
+        <v>2.19</v>
       </c>
       <c r="L1449">
-        <v>3.84</v>
+        <v>3.44</v>
       </c>
       <c r="M1449">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1449">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1449">
         <v>1</v>
@@ -74260,246 +74260,246 @@
     </row>
     <row r="1450" spans="1:16">
       <c r="A1450" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1450" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C1450">
-        <v>0.521044101995368</v>
+        <v>0.1288962489580445</v>
       </c>
       <c r="D1450" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E1450">
-        <v>0.2720261338532692</v>
+        <v>0.3705292581272586</v>
       </c>
       <c r="F1450">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1450">
-        <v>0.006158955898004631</v>
+        <v>0.006571103751041956</v>
       </c>
       <c r="H1450">
-        <v>0.006627973866146731</v>
+        <v>0.007369470741872742</v>
       </c>
       <c r="I1450">
-        <v>0.2490179681420988</v>
+        <v>0.241633009169214</v>
       </c>
       <c r="J1450">
-        <v>1.329696178304071</v>
+        <v>1.32555709919422</v>
       </c>
       <c r="K1450">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="L1450">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="M1450">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="N1450">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="O1450">
         <v>1</v>
       </c>
       <c r="P1450" t="s">
-        <v>221</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1451" spans="1:16">
       <c r="A1451" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B1451" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C1451">
-        <v>0.1156504395889431</v>
+        <v>0.1247179772158944</v>
       </c>
       <c r="D1451" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1451">
-        <v>0.4414805605988796</v>
+        <v>0.3705292581272586</v>
       </c>
       <c r="F1451">
         <v>1</v>
       </c>
       <c r="G1451">
-        <v>0.006684349560411057</v>
+        <v>0.007415282022784106</v>
       </c>
       <c r="H1451">
-        <v>0.006398519439401121</v>
+        <v>0.007369470741872742</v>
       </c>
       <c r="I1451">
-        <v>0.3258301210099366</v>
+        <v>0.2458112809113642</v>
       </c>
       <c r="J1451">
-        <v>1.329696178304071</v>
+        <v>1.32555709919422</v>
       </c>
       <c r="K1451">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="L1451">
-        <v>3.4</v>
+        <v>3.77</v>
       </c>
       <c r="M1451">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1451">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1451">
         <v>1</v>
       </c>
       <c r="P1451" t="s">
-        <v>221</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1452" spans="1:16">
       <c r="A1452" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B1452" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C1452">
-        <v>0.1256504395889433</v>
+        <v>0.1016956932481254</v>
       </c>
       <c r="D1452" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1452">
-        <v>0.4414805605988796</v>
+        <v>0.3705292581272586</v>
       </c>
       <c r="F1452">
         <v>1</v>
       </c>
       <c r="G1452">
-        <v>0.006694349560411057</v>
+        <v>0.007498304306751875</v>
       </c>
       <c r="H1452">
-        <v>0.006398519439401121</v>
+        <v>0.007369470741872742</v>
       </c>
       <c r="I1452">
-        <v>0.3158301210099363</v>
+        <v>0.2688335648791331</v>
       </c>
       <c r="J1452">
-        <v>1.329696178304071</v>
+        <v>1.32555709919422</v>
       </c>
       <c r="K1452">
-        <v>2.47</v>
+        <v>2.79</v>
       </c>
       <c r="L1452">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="M1452">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1452">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1452">
         <v>1</v>
       </c>
       <c r="P1452" t="s">
-        <v>221</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1453" spans="1:16">
       <c r="A1453" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B1453" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C1453">
-        <v>0.5212623312971241</v>
+        <v>0.1549512642400677</v>
       </c>
       <c r="D1453" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E1453">
-        <v>0.2612623312971243</v>
+        <v>0.3705292581272586</v>
       </c>
       <c r="F1453">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1453">
-        <v>0.006318737668702876</v>
+        <v>0.007525048735759932</v>
       </c>
       <c r="H1453">
-        <v>0.006058737668702876</v>
+        <v>0.007369470741872742</v>
       </c>
       <c r="I1453">
-        <v>0.2599999999999998</v>
+        <v>0.2155779938871909</v>
       </c>
       <c r="J1453">
-        <v>1.329696178304071</v>
+        <v>1.32555709919422</v>
       </c>
       <c r="K1453">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="L1453">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="M1453">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="N1453">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="O1453">
         <v>1</v>
       </c>
       <c r="P1453" t="s">
-        <v>221</v>
+        <v>476</v>
       </c>
     </row>
     <row r="1454" spans="1:16">
       <c r="A1454" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1454" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C1454">
-        <v>0.1188382867211062</v>
+        <v>0.521044101995368</v>
       </c>
       <c r="D1454" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E1454">
-        <v>0.3596020892772511</v>
+        <v>0.2720261338532692</v>
       </c>
       <c r="F1454">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1454">
-        <v>0.006581161713278894</v>
+        <v>0.006158955898004631</v>
       </c>
       <c r="H1454">
-        <v>0.007380397910722749</v>
+        <v>0.006627973866146731</v>
       </c>
       <c r="I1454">
-        <v>0.2407638025561449</v>
+        <v>0.2490179681420988</v>
       </c>
       <c r="J1454">
         <v>1.329696178304071</v>
       </c>
       <c r="K1454">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="L1454">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="M1454">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="N1454">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="O1454">
         <v>1</v>
@@ -74510,46 +74510,46 @@
     </row>
     <row r="1455" spans="1:16">
       <c r="A1455" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1455" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C1455">
-        <v>0.1133355096638033</v>
+        <v>0.1156504395889431</v>
       </c>
       <c r="D1455" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1455">
-        <v>0.3596020892772511</v>
+        <v>0.4414805605988796</v>
       </c>
       <c r="F1455">
         <v>1</v>
       </c>
       <c r="G1455">
-        <v>0.007426664490336197</v>
+        <v>0.006684349560411057</v>
       </c>
       <c r="H1455">
-        <v>0.007380397910722749</v>
+        <v>0.006398519439401121</v>
       </c>
       <c r="I1455">
-        <v>0.2462665796134478</v>
+        <v>0.3258301210099366</v>
       </c>
       <c r="J1455">
         <v>1.329696178304071</v>
       </c>
       <c r="K1455">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="L1455">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="M1455">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1455">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1455">
         <v>1</v>
@@ -74560,46 +74560,46 @@
     </row>
     <row r="1456" spans="1:16">
       <c r="A1456" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1456" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C1456">
-        <v>0.09014766253164019</v>
+        <v>0.1256504395889433</v>
       </c>
       <c r="D1456" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1456">
-        <v>0.3596020892772511</v>
+        <v>0.4414805605988796</v>
       </c>
       <c r="F1456">
         <v>1</v>
       </c>
       <c r="G1456">
-        <v>0.00750985233746836</v>
+        <v>0.006694349560411057</v>
       </c>
       <c r="H1456">
-        <v>0.007380397910722749</v>
+        <v>0.006398519439401121</v>
       </c>
       <c r="I1456">
-        <v>0.2694544267456109</v>
+        <v>0.3158301210099363</v>
       </c>
       <c r="J1456">
         <v>1.329696178304071</v>
       </c>
       <c r="K1456">
-        <v>2.79</v>
+        <v>2.47</v>
       </c>
       <c r="L1456">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="M1456">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1456">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1456">
         <v>1</v>
@@ -74610,46 +74610,46 @@
     </row>
     <row r="1457" spans="1:16">
       <c r="A1457" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1457" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C1457">
-        <v>0.1434446243146814</v>
+        <v>0.5212623312971241</v>
       </c>
       <c r="D1457" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E1457">
-        <v>0.3596020892772511</v>
+        <v>0.2612623312971243</v>
       </c>
       <c r="F1457">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1457">
-        <v>0.007536555375685318</v>
+        <v>0.006318737668702876</v>
       </c>
       <c r="H1457">
-        <v>0.007380397910722749</v>
+        <v>0.006058737668702876</v>
       </c>
       <c r="I1457">
-        <v>0.2161574649625697</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1457">
         <v>1.329696178304071</v>
       </c>
       <c r="K1457">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="L1457">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="M1457">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1457">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1457">
         <v>1</v>
@@ -74660,240 +74660,240 @@
     </row>
     <row r="1458" spans="1:16">
       <c r="A1458" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1458" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C1458">
-        <v>0.5673122132241386</v>
+        <v>0.5279653695140833</v>
       </c>
       <c r="D1458" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E1458">
-        <v>0.3241868818894775</v>
+        <v>0.2612623312971243</v>
       </c>
       <c r="F1458">
         <v>-1</v>
       </c>
       <c r="G1458">
-        <v>0.006112687786775862</v>
+        <v>0.006352034630485916</v>
       </c>
       <c r="H1458">
-        <v>0.006575813118110523</v>
+        <v>0.006058737668702876</v>
       </c>
       <c r="I1458">
-        <v>0.2431253313346611</v>
+        <v>0.2667030382169591</v>
       </c>
       <c r="J1458">
-        <v>1.307871597535784</v>
+        <v>1.329696178304071</v>
       </c>
       <c r="K1458">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="L1458">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="M1458">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="N1458">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="O1458">
         <v>1</v>
       </c>
       <c r="P1458" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1459" spans="1:16">
       <c r="A1459" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B1459" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C1459">
-        <v>0.1695571540866143</v>
+        <v>0.1188382867211062</v>
       </c>
       <c r="D1459" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1459">
-        <v>0.4903676215198445</v>
+        <v>0.3596020892772511</v>
       </c>
       <c r="F1459">
         <v>1</v>
       </c>
       <c r="G1459">
-        <v>0.006630442845913386</v>
+        <v>0.006581161713278894</v>
       </c>
       <c r="H1459">
-        <v>0.006349632378480155</v>
+        <v>0.007380397910722749</v>
       </c>
       <c r="I1459">
-        <v>0.3208104674332302</v>
+        <v>0.2407638025561449</v>
       </c>
       <c r="J1459">
-        <v>1.307871597535784</v>
+        <v>1.329696178304071</v>
       </c>
       <c r="K1459">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="L1459">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="M1459">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1459">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1459">
         <v>1</v>
       </c>
       <c r="P1459" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1460" spans="1:16">
       <c r="A1460" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B1460" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C1460">
-        <v>0.1795571540866145</v>
+        <v>0.1133355096638033</v>
       </c>
       <c r="D1460" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E1460">
-        <v>0.4903676215198445</v>
+        <v>0.3596020892772511</v>
       </c>
       <c r="F1460">
         <v>1</v>
       </c>
       <c r="G1460">
-        <v>0.006640442845913386</v>
+        <v>0.007426664490336197</v>
       </c>
       <c r="H1460">
-        <v>0.006349632378480155</v>
+        <v>0.007380397910722749</v>
       </c>
       <c r="I1460">
-        <v>0.3108104674332299</v>
+        <v>0.2462665796134478</v>
       </c>
       <c r="J1460">
-        <v>1.307871597535784</v>
+        <v>1.329696178304071</v>
       </c>
       <c r="K1460">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="L1460">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="M1460">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="N1460">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="O1460">
         <v>1</v>
       </c>
       <c r="P1460" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1461" spans="1:16">
       <c r="A1461" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1461" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C1461">
-        <v>0.5688399173719918</v>
+        <v>0.09014766253164019</v>
       </c>
       <c r="D1461" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E1461">
-        <v>0.308839917371992</v>
+        <v>0.3596020892772511</v>
       </c>
       <c r="F1461">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1461">
-        <v>0.006271160082628007</v>
+        <v>0.00750985233746836</v>
       </c>
       <c r="H1461">
-        <v>0.006011160082628008</v>
+        <v>0.007380397910722749</v>
       </c>
       <c r="I1461">
-        <v>0.2599999999999998</v>
+        <v>0.2694544267456109</v>
       </c>
       <c r="J1461">
-        <v>1.307871597535784</v>
+        <v>1.329696178304071</v>
       </c>
       <c r="K1461">
-        <v>2.18</v>
+        <v>2.79</v>
       </c>
       <c r="L1461">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="M1461">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="N1461">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="O1461">
         <v>1</v>
       </c>
       <c r="P1461" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1462" spans="1:16">
       <c r="A1462" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B1462" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C1462">
-        <v>0.1718720179880457</v>
+        <v>0.1434446243146814</v>
       </c>
       <c r="D1462" t="s">
         <v>347</v>
       </c>
       <c r="E1462">
-        <v>0.4172189825055312</v>
+        <v>0.3596020892772511</v>
       </c>
       <c r="F1462">
         <v>1</v>
       </c>
       <c r="G1462">
-        <v>0.006528127982011954</v>
+        <v>0.007536555375685318</v>
       </c>
       <c r="H1462">
-        <v>0.007322781017494469</v>
+        <v>0.007380397910722749</v>
       </c>
       <c r="I1462">
-        <v>0.2453469645174855</v>
+        <v>0.2161574649625697</v>
       </c>
       <c r="J1462">
-        <v>1.307871597535784</v>
+        <v>1.329696178304071</v>
       </c>
       <c r="K1462">
-        <v>2.43</v>
+        <v>2.78</v>
       </c>
       <c r="L1462">
-        <v>3.35</v>
+        <v>3.84</v>
       </c>
       <c r="M1462">
         <v>2.64</v>
@@ -74905,51 +74905,51 @@
         <v>1</v>
       </c>
       <c r="P1462" t="s">
-        <v>477</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1463" spans="1:16">
       <c r="A1463" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1463" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C1463">
-        <v>0.1733531067765952</v>
+        <v>0.5673122132241386</v>
       </c>
       <c r="D1463" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E1463">
-        <v>0.4172189825055312</v>
+        <v>0.3241868818894775</v>
       </c>
       <c r="F1463">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1463">
-        <v>0.007366646893223405</v>
+        <v>0.006112687786775862</v>
       </c>
       <c r="H1463">
-        <v>0.007322781017494469</v>
+        <v>0.006575813118110523</v>
       </c>
       <c r="I1463">
-        <v>0.243865875728936</v>
+        <v>0.2431253313346611</v>
       </c>
       <c r="J1463">
         <v>1.307871597535784</v>
       </c>
       <c r="K1463">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="L1463">
-        <v>3.77</v>
+        <v>3.34</v>
       </c>
       <c r="M1463">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="N1463">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="O1463">
         <v>1</v>
@@ -74960,46 +74960,46 @@
     </row>
     <row r="1464" spans="1:16">
       <c r="A1464" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1464" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C1464">
-        <v>0.1510382428751638</v>
+        <v>0.1695571540866143</v>
       </c>
       <c r="D1464" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1464">
-        <v>0.4172189825055312</v>
+        <v>0.4903676215198445</v>
       </c>
       <c r="F1464">
         <v>1</v>
       </c>
       <c r="G1464">
-        <v>0.007448961757124836</v>
+        <v>0.006630442845913386</v>
       </c>
       <c r="H1464">
-        <v>0.007322781017494469</v>
+        <v>0.006349632378480155</v>
       </c>
       <c r="I1464">
-        <v>0.2661807396303675</v>
+        <v>0.3208104674332302</v>
       </c>
       <c r="J1464">
         <v>1.307871597535784</v>
       </c>
       <c r="K1464">
-        <v>2.79</v>
+        <v>2.47</v>
       </c>
       <c r="L1464">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="M1464">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1464">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1464">
         <v>1</v>
@@ -75010,290 +75010,290 @@
     </row>
     <row r="1465" spans="1:16">
       <c r="A1465" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1465" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C1465">
-        <v>0.6676280159287886</v>
+        <v>0.1795571540866145</v>
       </c>
       <c r="D1465" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E1465">
-        <v>0.4372787538065124</v>
+        <v>0.4903676215198445</v>
       </c>
       <c r="F1465">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1465">
-        <v>0.006012371984071212</v>
+        <v>0.006640442845913386</v>
       </c>
       <c r="H1465">
-        <v>0.006462721246193488</v>
+        <v>0.006349632378480155</v>
       </c>
       <c r="I1465">
-        <v>0.2303492621222762</v>
+        <v>0.3108104674332299</v>
       </c>
       <c r="J1465">
-        <v>1.260552822675099</v>
+        <v>1.307871597535784</v>
       </c>
       <c r="K1465">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="L1465">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="M1465">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="N1465">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="O1465">
         <v>1</v>
       </c>
       <c r="P1465" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1466" spans="1:16">
       <c r="A1466" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1466" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C1466">
-        <v>0.2864345279925038</v>
+        <v>0.5688399173719918</v>
       </c>
       <c r="D1466" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1466">
-        <v>0.5963616772077769</v>
+        <v>0.308839917371992</v>
       </c>
       <c r="F1466">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1466">
-        <v>0.006513565472007496</v>
+        <v>0.006271160082628007</v>
       </c>
       <c r="H1466">
-        <v>0.006243638322792223</v>
+        <v>0.006011160082628008</v>
       </c>
       <c r="I1466">
-        <v>0.3099271492152731</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="J1466">
-        <v>1.260552822675099</v>
+        <v>1.307871597535784</v>
       </c>
       <c r="K1466">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="L1466">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="M1466">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="N1466">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="O1466">
         <v>1</v>
       </c>
       <c r="P1466" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1467" spans="1:16">
       <c r="A1467" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1467" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C1467">
-        <v>0.296434527992504</v>
+        <v>0.575761201396634</v>
       </c>
       <c r="D1467" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1467">
-        <v>0.5963616772077769</v>
+        <v>0.308839917371992</v>
       </c>
       <c r="F1467">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1467">
-        <v>0.006523565472007496</v>
+        <v>0.006304238798603367</v>
       </c>
       <c r="H1467">
-        <v>0.006243638322792223</v>
+        <v>0.006011160082628008</v>
       </c>
       <c r="I1467">
-        <v>0.2999271492152729</v>
+        <v>0.266921284024642</v>
       </c>
       <c r="J1467">
-        <v>1.260552822675099</v>
+        <v>1.307871597535784</v>
       </c>
       <c r="K1467">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="L1467">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="M1467">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="N1467">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="O1467">
         <v>1</v>
       </c>
       <c r="P1467" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1468" spans="1:16">
       <c r="A1468" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1468" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C1468">
-        <v>0.6719948465682828</v>
+        <v>0.1718720179880457</v>
       </c>
       <c r="D1468" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E1468">
-        <v>0.411994846568283</v>
+        <v>0.4172189825055312</v>
       </c>
       <c r="F1468">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1468">
-        <v>0.006168005153431717</v>
+        <v>0.006528127982011954</v>
       </c>
       <c r="H1468">
-        <v>0.005908005153431717</v>
+        <v>0.007322781017494469</v>
       </c>
       <c r="I1468">
-        <v>0.2599999999999998</v>
+        <v>0.2453469645174855</v>
       </c>
       <c r="J1468">
-        <v>1.260552822675099</v>
+        <v>1.307871597535784</v>
       </c>
       <c r="K1468">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="L1468">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="M1468">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="N1468">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="O1468">
         <v>1</v>
       </c>
       <c r="P1468" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1469" spans="1:16">
       <c r="A1469" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1469" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C1469">
-        <v>0.6793893183415323</v>
+        <v>0.1733531067765952</v>
       </c>
       <c r="D1469" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E1469">
-        <v>0.411994846568283</v>
+        <v>0.4172189825055312</v>
       </c>
       <c r="F1469">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1469">
-        <v>0.006200610681658468</v>
+        <v>0.007366646893223405</v>
       </c>
       <c r="H1469">
-        <v>0.005908005153431717</v>
+        <v>0.007322781017494469</v>
       </c>
       <c r="I1469">
-        <v>0.2673944717732493</v>
+        <v>0.243865875728936</v>
       </c>
       <c r="J1469">
-        <v>1.260552822675099</v>
+        <v>1.307871597535784</v>
       </c>
       <c r="K1469">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="L1469">
-        <v>3.44</v>
+        <v>3.77</v>
       </c>
       <c r="M1469">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="N1469">
-        <v>3.16</v>
+        <v>3.87</v>
       </c>
       <c r="O1469">
         <v>1</v>
       </c>
       <c r="P1469" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1470" spans="1:16">
       <c r="A1470" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1470" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C1470">
-        <v>0.2868566408995079</v>
+        <v>0.1510382428751638</v>
       </c>
       <c r="D1470" t="s">
         <v>347</v>
       </c>
       <c r="E1470">
-        <v>0.5421405481377373</v>
+        <v>0.4172189825055312</v>
       </c>
       <c r="F1470">
         <v>1</v>
       </c>
       <c r="G1470">
-        <v>0.006413143359100492</v>
+        <v>0.007448961757124836</v>
       </c>
       <c r="H1470">
-        <v>0.007197859451862263</v>
+        <v>0.007322781017494469</v>
       </c>
       <c r="I1470">
-        <v>0.2552839072382294</v>
+        <v>0.2661807396303675</v>
       </c>
       <c r="J1470">
-        <v>1.260552822675099</v>
+        <v>1.307871597535784</v>
       </c>
       <c r="K1470">
-        <v>2.43</v>
+        <v>2.79</v>
       </c>
       <c r="L1470">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="M1470">
         <v>2.64</v>
@@ -75305,51 +75305,51 @@
         <v>1</v>
       </c>
       <c r="P1470" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1471" spans="1:16">
       <c r="A1471" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1471" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C1471">
-        <v>0.3034797376434764</v>
+        <v>0.6676280159287886</v>
       </c>
       <c r="D1471" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E1471">
-        <v>0.5421405481377373</v>
+        <v>0.4372787538065124</v>
       </c>
       <c r="F1471">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1471">
-        <v>0.007236520262356523</v>
+        <v>0.006012371984071212</v>
       </c>
       <c r="H1471">
-        <v>0.007197859451862263</v>
+        <v>0.006462721246193488</v>
       </c>
       <c r="I1471">
-        <v>0.2386608104942609</v>
+        <v>0.2303492621222762</v>
       </c>
       <c r="J1471">
         <v>1.260552822675099</v>
       </c>
       <c r="K1471">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="L1471">
-        <v>3.77</v>
+        <v>3.34</v>
       </c>
       <c r="M1471">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="N1471">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
       <c r="O1471">
         <v>1</v>
@@ -75360,46 +75360,46 @@
     </row>
     <row r="1472" spans="1:16">
       <c r="A1472" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B1472" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C1472">
-        <v>0.2830576247364722</v>
+        <v>0.2864345279925038</v>
       </c>
       <c r="D1472" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E1472">
-        <v>0.5421405481377373</v>
+        <v>0.5963616772077769</v>
       </c>
       <c r="F1472">
         <v>1</v>
       </c>
       <c r="G1472">
-        <v>0.007316942375263528</v>
+        <v>0.006513565472007496</v>
       </c>
       <c r="H1472">
-        <v>0.007197859451862263</v>
+        <v>0.006243638322792223</v>
       </c>
       <c r="I1472">
-        <v>0.259082923401265</v>
+        <v>0.3099271492152731</v>
       </c>
       <c r="J1472">
         <v>1.260552822675099</v>
       </c>
       <c r="K1472">
-        <v>2.79</v>
+        <v>2.47</v>
       </c>
       <c r="L1472">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="M1472">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="N1472">
-        <v>3.87</v>
+        <v>3.42</v>
       </c>
       <c r="O1472">
         <v>1</v>
@@ -75410,51 +75410,351 @@
     </row>
     <row r="1473" spans="1:16">
       <c r="A1473" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B1473" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C1473">
-        <v>0.6762309674396816</v>
+        <v>0.296434527992504</v>
       </c>
       <c r="D1473" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="E1473">
-        <v>0.6574973061606935</v>
+        <v>0.5963616772077769</v>
       </c>
       <c r="F1473">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1473">
-        <v>0.008743769032560319</v>
+        <v>0.006523565472007496</v>
       </c>
       <c r="H1473">
-        <v>0.008422502693839306</v>
+        <v>0.006243638322792223</v>
       </c>
       <c r="I1473">
-        <v>0.01873366127898812</v>
+        <v>0.2999271492152729</v>
       </c>
       <c r="J1473">
         <v>1.260552822675099</v>
       </c>
       <c r="K1473">
+        <v>2.47</v>
+      </c>
+      <c r="L1473">
+        <v>3.41</v>
+      </c>
+      <c r="M1473">
+        <v>2.24</v>
+      </c>
+      <c r="N1473">
+        <v>3.42</v>
+      </c>
+      <c r="O1473">
+        <v>1</v>
+      </c>
+      <c r="P1473" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:16">
+      <c r="A1474" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1474">
+        <v>0.6719948465682828</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1474">
+        <v>0.411994846568283</v>
+      </c>
+      <c r="F1474">
+        <v>-1</v>
+      </c>
+      <c r="G1474">
+        <v>0.006168005153431717</v>
+      </c>
+      <c r="H1474">
+        <v>0.005908005153431717</v>
+      </c>
+      <c r="I1474">
+        <v>0.2599999999999998</v>
+      </c>
+      <c r="J1474">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1474">
+        <v>2.18</v>
+      </c>
+      <c r="L1474">
+        <v>3.42</v>
+      </c>
+      <c r="M1474">
+        <v>2.18</v>
+      </c>
+      <c r="N1474">
+        <v>3.16</v>
+      </c>
+      <c r="O1474">
+        <v>1</v>
+      </c>
+      <c r="P1474" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:16">
+      <c r="A1475" s="1">
+        <v>4</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1475">
+        <v>0.6793893183415323</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1475">
+        <v>0.411994846568283</v>
+      </c>
+      <c r="F1475">
+        <v>-1</v>
+      </c>
+      <c r="G1475">
+        <v>0.006200610681658468</v>
+      </c>
+      <c r="H1475">
+        <v>0.005908005153431717</v>
+      </c>
+      <c r="I1475">
+        <v>0.2673944717732493</v>
+      </c>
+      <c r="J1475">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1475">
+        <v>2.19</v>
+      </c>
+      <c r="L1475">
+        <v>3.44</v>
+      </c>
+      <c r="M1475">
+        <v>2.18</v>
+      </c>
+      <c r="N1475">
+        <v>3.16</v>
+      </c>
+      <c r="O1475">
+        <v>1</v>
+      </c>
+      <c r="P1475" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:16">
+      <c r="A1476" s="1">
+        <v>5</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1476">
+        <v>0.2868566408995079</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1476">
+        <v>0.5421405481377373</v>
+      </c>
+      <c r="F1476">
+        <v>1</v>
+      </c>
+      <c r="G1476">
+        <v>0.006413143359100492</v>
+      </c>
+      <c r="H1476">
+        <v>0.007197859451862263</v>
+      </c>
+      <c r="I1476">
+        <v>0.2552839072382294</v>
+      </c>
+      <c r="J1476">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1476">
+        <v>2.43</v>
+      </c>
+      <c r="L1476">
+        <v>3.35</v>
+      </c>
+      <c r="M1476">
+        <v>2.64</v>
+      </c>
+      <c r="N1476">
+        <v>3.87</v>
+      </c>
+      <c r="O1476">
+        <v>1</v>
+      </c>
+      <c r="P1476" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:16">
+      <c r="A1477" s="1">
+        <v>6</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1477">
+        <v>0.3034797376434764</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1477">
+        <v>0.5421405481377373</v>
+      </c>
+      <c r="F1477">
+        <v>1</v>
+      </c>
+      <c r="G1477">
+        <v>0.007236520262356523</v>
+      </c>
+      <c r="H1477">
+        <v>0.007197859451862263</v>
+      </c>
+      <c r="I1477">
+        <v>0.2386608104942609</v>
+      </c>
+      <c r="J1477">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1477">
+        <v>2.75</v>
+      </c>
+      <c r="L1477">
+        <v>3.77</v>
+      </c>
+      <c r="M1477">
+        <v>2.64</v>
+      </c>
+      <c r="N1477">
+        <v>3.87</v>
+      </c>
+      <c r="O1477">
+        <v>1</v>
+      </c>
+      <c r="P1477" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:16">
+      <c r="A1478" s="1">
+        <v>7</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1478">
+        <v>0.2830576247364722</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1478">
+        <v>0.5421405481377373</v>
+      </c>
+      <c r="F1478">
+        <v>1</v>
+      </c>
+      <c r="G1478">
+        <v>0.007316942375263528</v>
+      </c>
+      <c r="H1478">
+        <v>0.007197859451862263</v>
+      </c>
+      <c r="I1478">
+        <v>0.259082923401265</v>
+      </c>
+      <c r="J1478">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1478">
+        <v>2.79</v>
+      </c>
+      <c r="L1478">
+        <v>3.8</v>
+      </c>
+      <c r="M1478">
+        <v>2.64</v>
+      </c>
+      <c r="N1478">
+        <v>3.87</v>
+      </c>
+      <c r="O1478">
+        <v>1</v>
+      </c>
+      <c r="P1478" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:16">
+      <c r="A1479" s="1">
+        <v>8</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1479">
+        <v>0.6762309674396816</v>
+      </c>
+      <c r="D1479" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1479">
+        <v>0.862286249707191</v>
+      </c>
+      <c r="F1479">
+        <v>-1</v>
+      </c>
+      <c r="G1479">
+        <v>0.008743769032560319</v>
+      </c>
+      <c r="H1479">
+        <v>0.008677713750292809</v>
+      </c>
+      <c r="I1479">
+        <v>-0.1860552822675094</v>
+      </c>
+      <c r="J1479">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1479">
         <v>3.2</v>
       </c>
-      <c r="L1473">
+      <c r="L1479">
         <v>4.71</v>
       </c>
-      <c r="M1473">
-        <v>3.08</v>
-      </c>
-      <c r="N1473">
-        <v>4.54</v>
-      </c>
-      <c r="O1473">
-        <v>1</v>
-      </c>
-      <c r="P1473" t="s">
+      <c r="M1479">
+        <v>3.1</v>
+      </c>
+      <c r="N1479">
+        <v>4.77</v>
+      </c>
+      <c r="O1479">
+        <v>1</v>
+      </c>
+      <c r="P1479" t="s">
         <v>478</v>
       </c>
     </row>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -74430,10 +74430,10 @@
         <v>0</v>
       </c>
       <c r="B1454" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C1454">
-        <v>0.5673122132241386</v>
+        <v>0.6173122132241389</v>
       </c>
       <c r="D1454" t="s">
         <v>328</v>
@@ -74445,13 +74445,13 @@
         <v>-1</v>
       </c>
       <c r="G1454">
-        <v>0.006112687786775862</v>
+        <v>0.006162687786775862</v>
       </c>
       <c r="H1454">
         <v>0.006575813118110523</v>
       </c>
       <c r="I1454">
-        <v>0.2431253313346611</v>
+        <v>0.2931253313346613</v>
       </c>
       <c r="J1454">
         <v>1.307871597535784</v>
@@ -74460,7 +74460,7 @@
         <v>2.12</v>
       </c>
       <c r="L1454">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="M1454">
         <v>2.39</v>
@@ -74630,10 +74630,10 @@
         <v>4</v>
       </c>
       <c r="B1458" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C1458">
-        <v>0.5688399173719918</v>
+        <v>0.5919186333473498</v>
       </c>
       <c r="D1458" t="s">
         <v>330</v>
@@ -74645,22 +74645,22 @@
         <v>-1</v>
       </c>
       <c r="G1458">
-        <v>0.006271160082628007</v>
+        <v>0.00626808136665265</v>
       </c>
       <c r="H1458">
         <v>0.006011160082628008</v>
       </c>
       <c r="I1458">
-        <v>0.2599999999999998</v>
+        <v>0.2830787159753578</v>
       </c>
       <c r="J1458">
         <v>1.307871597535784</v>
       </c>
       <c r="K1458">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="L1458">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="M1458">
         <v>2.18</v>
@@ -75180,10 +75180,10 @@
         <v>5</v>
       </c>
       <c r="B1469" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C1469">
-        <v>0.6793893183415323</v>
+        <v>0.7246003747950343</v>
       </c>
       <c r="D1469" t="s">
         <v>330</v>
@@ -75195,22 +75195,22 @@
         <v>-1</v>
       </c>
       <c r="G1469">
-        <v>0.006200610681658468</v>
+        <v>0.006195399625204966</v>
       </c>
       <c r="H1469">
         <v>0.005908005153431717</v>
       </c>
       <c r="I1469">
-        <v>0.2673944717732493</v>
+        <v>0.3126055282267513</v>
       </c>
       <c r="J1469">
         <v>1.260552822675099</v>
       </c>
       <c r="K1469">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="L1469">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="M1469">
         <v>2.18</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4431" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="468">
   <si>
     <t>trade_time</t>
   </si>
@@ -1775,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1473"/>
+  <dimension ref="A1:P1474"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -75180,10 +75180,10 @@
         <v>5</v>
       </c>
       <c r="B1469" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C1469">
-        <v>0.7246003747950343</v>
+        <v>0.727205903021785</v>
       </c>
       <c r="D1469" t="s">
         <v>330</v>
@@ -75195,22 +75195,22 @@
         <v>-1</v>
       </c>
       <c r="G1469">
-        <v>0.006195399625204966</v>
+        <v>0.006172794096978215</v>
       </c>
       <c r="H1469">
         <v>0.005908005153431717</v>
       </c>
       <c r="I1469">
-        <v>0.3126055282267513</v>
+        <v>0.315211056453502</v>
       </c>
       <c r="J1469">
         <v>1.260552822675099</v>
       </c>
       <c r="K1469">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="L1469">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="M1469">
         <v>2.18</v>
@@ -75230,43 +75230,43 @@
         <v>6</v>
       </c>
       <c r="B1470" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C1470">
-        <v>0.2868566408995079</v>
+        <v>0.7246003747950343</v>
       </c>
       <c r="D1470" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="E1470">
-        <v>0.5421405481377373</v>
+        <v>0.411994846568283</v>
       </c>
       <c r="F1470">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1470">
-        <v>0.006413143359100492</v>
+        <v>0.006195399625204966</v>
       </c>
       <c r="H1470">
-        <v>0.007197859451862263</v>
+        <v>0.005908005153431717</v>
       </c>
       <c r="I1470">
-        <v>0.2552839072382294</v>
+        <v>0.3126055282267513</v>
       </c>
       <c r="J1470">
         <v>1.260552822675099</v>
       </c>
       <c r="K1470">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="L1470">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="M1470">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="N1470">
-        <v>3.87</v>
+        <v>3.16</v>
       </c>
       <c r="O1470">
         <v>1</v>
@@ -75280,10 +75280,10 @@
         <v>7</v>
       </c>
       <c r="B1471" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C1471">
-        <v>0.3034797376434764</v>
+        <v>0.2868566408995079</v>
       </c>
       <c r="D1471" t="s">
         <v>336</v>
@@ -75295,22 +75295,22 @@
         <v>1</v>
       </c>
       <c r="G1471">
-        <v>0.007236520262356523</v>
+        <v>0.006413143359100492</v>
       </c>
       <c r="H1471">
         <v>0.007197859451862263</v>
       </c>
       <c r="I1471">
-        <v>0.2386608104942609</v>
+        <v>0.2552839072382294</v>
       </c>
       <c r="J1471">
         <v>1.260552822675099</v>
       </c>
       <c r="K1471">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="L1471">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="M1471">
         <v>2.64</v>
@@ -75330,10 +75330,10 @@
         <v>8</v>
       </c>
       <c r="B1472" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C1472">
-        <v>0.2830576247364722</v>
+        <v>0.3034797376434764</v>
       </c>
       <c r="D1472" t="s">
         <v>336</v>
@@ -75345,22 +75345,22 @@
         <v>1</v>
       </c>
       <c r="G1472">
-        <v>0.007316942375263528</v>
+        <v>0.007236520262356523</v>
       </c>
       <c r="H1472">
         <v>0.007197859451862263</v>
       </c>
       <c r="I1472">
-        <v>0.259082923401265</v>
+        <v>0.2386608104942609</v>
       </c>
       <c r="J1472">
         <v>1.260552822675099</v>
       </c>
       <c r="K1472">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="L1472">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="M1472">
         <v>2.64</v>
@@ -75380,48 +75380,98 @@
         <v>9</v>
       </c>
       <c r="B1473" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1473">
-        <v>0.862286249707191</v>
+        <v>0.2830576247364722</v>
       </c>
       <c r="D1473" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E1473">
-        <v>1.010102834387445</v>
+        <v>0.5421405481377373</v>
       </c>
       <c r="F1473">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1473">
-        <v>0.008677713750292809</v>
+        <v>0.007316942375263528</v>
       </c>
       <c r="H1473">
-        <v>0.008749897165612556</v>
+        <v>0.007197859451862263</v>
       </c>
       <c r="I1473">
-        <v>-0.1478165846802537</v>
+        <v>0.259082923401265</v>
       </c>
       <c r="J1473">
         <v>1.260552822675099</v>
       </c>
       <c r="K1473">
+        <v>2.79</v>
+      </c>
+      <c r="L1473">
+        <v>3.8</v>
+      </c>
+      <c r="M1473">
+        <v>2.64</v>
+      </c>
+      <c r="N1473">
+        <v>3.87</v>
+      </c>
+      <c r="O1473">
+        <v>1</v>
+      </c>
+      <c r="P1473" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:16">
+      <c r="A1474" s="1">
+        <v>10</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1474">
+        <v>0.862286249707191</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1474">
+        <v>1.010102834387445</v>
+      </c>
+      <c r="F1474">
+        <v>-1</v>
+      </c>
+      <c r="G1474">
+        <v>0.008677713750292809</v>
+      </c>
+      <c r="H1474">
+        <v>0.008749897165612556</v>
+      </c>
+      <c r="I1474">
+        <v>-0.1478165846802537</v>
+      </c>
+      <c r="J1474">
+        <v>1.260552822675099</v>
+      </c>
+      <c r="K1474">
         <v>3.1</v>
       </c>
-      <c r="L1473">
+      <c r="L1474">
         <v>4.77</v>
       </c>
-      <c r="M1473">
+      <c r="M1474">
         <v>3.07</v>
       </c>
-      <c r="N1473">
+      <c r="N1474">
         <v>4.88</v>
       </c>
-      <c r="O1473">
-        <v>1</v>
-      </c>
-      <c r="P1473" t="s">
+      <c r="O1474">
+        <v>1</v>
+      </c>
+      <c r="P1474" t="s">
         <v>467</v>
       </c>
     </row>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -709,7 +709,7 @@
     <t>2021-09-28</t>
   </si>
   <si>
-    <t>2021-10-08</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2016-07-28</t>
@@ -1051,10 +1051,10 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-29</t>
+    <t>2021-09-30</t>
   </si>
   <si>
-    <t>2021-10-12</t>
+    <t>2021-10-18</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75507,7 +75507,7 @@
         <v>345</v>
       </c>
       <c r="E1475">
-        <v>0.7515201441741861</v>
+        <v>0.5892240472995525</v>
       </c>
       <c r="F1475">
         <v>-1</v>
@@ -75516,10 +75516,10 @@
         <v>0.009580775952700449</v>
       </c>
       <c r="H1475">
-        <v>0.008648479855825814</v>
+        <v>0.008870775952700449</v>
       </c>
       <c r="I1475">
-        <v>0.5477039031253663</v>
+        <v>0.71</v>
       </c>
       <c r="J1475">
         <v>1.281973979164225</v>
@@ -75531,10 +75531,10 @@
         <v>5.44</v>
       </c>
       <c r="M1475">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="N1475">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="O1475">
         <v>1</v>
@@ -75557,7 +75557,7 @@
         <v>345</v>
       </c>
       <c r="E1476">
-        <v>0.7515201441741861</v>
+        <v>0.5892240472995525</v>
       </c>
       <c r="F1476">
         <v>-1</v>
@@ -75566,10 +75566,10 @@
         <v>0.008794381156867603</v>
       </c>
       <c r="H1476">
-        <v>0.008648479855825814</v>
+        <v>0.008870775952700449</v>
       </c>
       <c r="I1476">
-        <v>0.2740986989582117</v>
+        <v>0.4363947958328454</v>
       </c>
       <c r="J1476">
         <v>1.281973979164225</v>
@@ -75581,10 +75581,10 @@
         <v>4.91</v>
       </c>
       <c r="M1476">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="N1476">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="O1476">
         <v>1</v>
@@ -75601,40 +75601,40 @@
         <v>231</v>
       </c>
       <c r="C1477">
-        <v>0.4784385829240394</v>
+        <v>0.2571596237574703</v>
       </c>
       <c r="D1477" t="s">
         <v>346</v>
       </c>
       <c r="E1477">
-        <v>0.2571596237574703</v>
+        <v>0.3779149400070314</v>
       </c>
       <c r="F1477">
         <v>1</v>
       </c>
       <c r="G1477">
-        <v>0.008221561417075961</v>
+        <v>0.008102840376242528</v>
       </c>
       <c r="H1477">
-        <v>0.008102840376242528</v>
+        <v>0.00776208505999297</v>
       </c>
       <c r="I1477">
-        <v>-0.2212789591665691</v>
+        <v>0.1207553162495612</v>
       </c>
       <c r="J1477">
         <v>1.281973979164225</v>
       </c>
       <c r="K1477">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="L1477">
-        <v>4.35</v>
+        <v>4.18</v>
       </c>
       <c r="M1477">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="N1477">
-        <v>4.18</v>
+        <v>4.07</v>
       </c>
       <c r="O1477">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1054,7 +1054,7 @@
     <t>2021-09-30</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75607,7 +75607,7 @@
         <v>346</v>
       </c>
       <c r="E1477">
-        <v>0.3779149400070314</v>
+        <v>0.3138162410488201</v>
       </c>
       <c r="F1477">
         <v>1</v>
@@ -75616,10 +75616,10 @@
         <v>0.008102840376242528</v>
       </c>
       <c r="H1477">
-        <v>0.00776208505999297</v>
+        <v>0.00782618375895118</v>
       </c>
       <c r="I1477">
-        <v>0.1207553162495612</v>
+        <v>0.05665661729134985</v>
       </c>
       <c r="J1477">
         <v>1.281973979164225</v>
@@ -75631,7 +75631,7 @@
         <v>4.18</v>
       </c>
       <c r="M1477">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="N1477">
         <v>4.07</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1057,7 +1057,7 @@
     <t>2021-09-30</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75610,7 +75610,7 @@
         <v>347</v>
       </c>
       <c r="E1477">
-        <v>0.5058806645909018</v>
+        <v>0.6540780625073239</v>
       </c>
       <c r="F1477">
         <v>1</v>
@@ -75619,10 +75619,10 @@
         <v>0.008102840376242528</v>
       </c>
       <c r="H1477">
-        <v>0.008454119335409099</v>
+        <v>0.008345921937492676</v>
       </c>
       <c r="I1477">
-        <v>0.2487210408334315</v>
+        <v>0.3969184387498537</v>
       </c>
       <c r="J1477">
         <v>1.281973979164225</v>
@@ -75634,10 +75634,10 @@
         <v>4.18</v>
       </c>
       <c r="M1477">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N1477">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="O1477">
         <v>1</v>
@@ -75660,7 +75660,7 @@
         <v>347</v>
       </c>
       <c r="E1478">
-        <v>0.5058806645909018</v>
+        <v>0.6540780625073239</v>
       </c>
       <c r="F1478">
         <v>1</v>
@@ -75669,10 +75669,10 @@
         <v>0.00782618375895118</v>
       </c>
       <c r="H1478">
-        <v>0.008454119335409099</v>
+        <v>0.008345921937492676</v>
       </c>
       <c r="I1478">
-        <v>0.1920644235420816</v>
+        <v>0.3402618214585038</v>
       </c>
       <c r="J1478">
         <v>1.281973979164225</v>
@@ -75684,10 +75684,10 @@
         <v>4.07</v>
       </c>
       <c r="M1478">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N1478">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="O1478">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1060,7 +1060,7 @@
     <t>2021-10-20</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-10-26</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75713,7 +75713,7 @@
         <v>348</v>
       </c>
       <c r="E1479">
-        <v>-0.249743849921729</v>
+        <v>-0.115367306088257</v>
       </c>
       <c r="F1479">
         <v>-1</v>
@@ -75722,10 +75722,10 @@
         <v>0.009164120393755202</v>
       </c>
       <c r="H1479">
-        <v>0.008829743849921729</v>
+        <v>0.008715367306088257</v>
       </c>
       <c r="I1479">
-        <v>0.08562345616652767</v>
+        <v>-0.04875308766694442</v>
       </c>
       <c r="J1479">
         <v>1.5547067979184</v>
@@ -75737,10 +75737,10 @@
         <v>4.5</v>
       </c>
       <c r="M1479">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="N1479">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="O1479">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -712,7 +712,7 @@
     <t>2021-10-12</t>
   </si>
   <si>
-    <t>2021-10-21</t>
+    <t>2021-10-26</t>
   </si>
   <si>
     <t>2016-07-28</t>
@@ -1057,10 +1057,10 @@
     <t>2021-09-30</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-27</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75610,10 +75610,10 @@
         <v>0.2571596237574703</v>
       </c>
       <c r="D1477" t="s">
-        <v>232</v>
+        <v>347</v>
       </c>
       <c r="E1477">
-        <v>0.6540780625073239</v>
+        <v>0.821258322715682</v>
       </c>
       <c r="F1477">
         <v>1</v>
@@ -75622,10 +75622,10 @@
         <v>0.008102840376242528</v>
       </c>
       <c r="H1477">
-        <v>0.008345921937492676</v>
+        <v>0.008538741677284318</v>
       </c>
       <c r="I1477">
-        <v>0.3969184387498537</v>
+        <v>0.5640986989582117</v>
       </c>
       <c r="J1477">
         <v>1.281973979164225</v>
@@ -75637,10 +75637,10 @@
         <v>4.18</v>
       </c>
       <c r="M1477">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="N1477">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="O1477">
         <v>1</v>
@@ -75660,10 +75660,10 @@
         <v>-0.5774028016303054</v>
       </c>
       <c r="D1478" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1478">
-        <v>-0.3395910735470409</v>
+        <v>-0.1641203937552014</v>
       </c>
       <c r="F1478">
         <v>1</v>
@@ -75672,10 +75672,10 @@
         <v>0.008937402801630306</v>
       </c>
       <c r="H1478">
-        <v>0.009299591073547041</v>
+        <v>0.009164120393755202</v>
       </c>
       <c r="I1478">
-        <v>0.2378117280832646</v>
+        <v>0.4132824078751041</v>
       </c>
       <c r="J1478">
         <v>1.5547067979184</v>
@@ -75687,10 +75687,10 @@
         <v>4.18</v>
       </c>
       <c r="M1478">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N1478">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="O1478">
         <v>1</v>
@@ -75707,40 +75707,40 @@
         <v>232</v>
       </c>
       <c r="C1479">
-        <v>-0.1641203937552014</v>
+        <v>-0.115367306088257</v>
       </c>
       <c r="D1479" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E1479">
-        <v>-0.115367306088257</v>
+        <v>0.0003325382656145237</v>
       </c>
       <c r="F1479">
         <v>-1</v>
       </c>
       <c r="G1479">
-        <v>0.009164120393755202</v>
+        <v>0.008715367306088257</v>
       </c>
       <c r="H1479">
-        <v>0.008715367306088257</v>
+        <v>0.009359667461734385</v>
       </c>
       <c r="I1479">
-        <v>-0.04875308766694442</v>
+        <v>-0.1156998443538715</v>
       </c>
       <c r="J1479">
         <v>1.5547067979184</v>
       </c>
       <c r="K1479">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="L1479">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="M1479">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="N1479">
-        <v>4.3</v>
+        <v>4.68</v>
       </c>
       <c r="O1479">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -715,7 +715,7 @@
     <t>2021-10-19</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-27</t>
   </si>
   <si>
     <t>2016-07-28</t>
@@ -1057,16 +1057,16 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-30</t>
+    <t>2021-09-23</t>
   </si>
   <si>
-    <t>2021-10-27</t>
+    <t>2021-09-30</t>
   </si>
   <si>
     <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-10-28</t>
+    <t>2021-11-01</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75519,7 +75519,7 @@
         <v>347</v>
       </c>
       <c r="E1475">
-        <v>0.5892240472995525</v>
+        <v>1.299224047299552</v>
       </c>
       <c r="F1475">
         <v>-1</v>
@@ -75528,10 +75528,10 @@
         <v>0.008197986361034759</v>
       </c>
       <c r="H1475">
-        <v>0.008870775952700449</v>
+        <v>0.009580775952700449</v>
       </c>
       <c r="I1475">
-        <v>0.3527895916656902</v>
+        <v>-0.3572104083343097</v>
       </c>
       <c r="J1475">
         <v>1.281973979164225</v>
@@ -75546,7 +75546,7 @@
         <v>3.23</v>
       </c>
       <c r="N1475">
-        <v>4.73</v>
+        <v>5.44</v>
       </c>
       <c r="O1475">
         <v>1</v>
@@ -75566,7 +75566,7 @@
         <v>0.9425372818822506</v>
       </c>
       <c r="D1476" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1476">
         <v>0.5892240472995525</v>
@@ -75616,7 +75616,7 @@
         <v>0.2571596237574703</v>
       </c>
       <c r="D1477" t="s">
-        <v>348</v>
+        <v>233</v>
       </c>
       <c r="E1477">
         <v>0.821258322715682</v>
@@ -75702,7 +75702,7 @@
         <v>1</v>
       </c>
       <c r="P1478" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1479" spans="1:16">
@@ -75752,7 +75752,7 @@
         <v>1</v>
       </c>
       <c r="P1479" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1480" spans="1:16">
@@ -75763,46 +75763,46 @@
         <v>233</v>
       </c>
       <c r="C1480">
-        <v>-0.115367306088257</v>
+        <v>0.0003325382656145237</v>
       </c>
       <c r="D1480" t="s">
         <v>350</v>
       </c>
       <c r="E1480">
-        <v>-0.03529091790091421</v>
+        <v>-0.3019321218384654</v>
       </c>
       <c r="F1480">
         <v>-1</v>
       </c>
       <c r="G1480">
-        <v>0.008715367306088257</v>
+        <v>0.009359667461734385</v>
       </c>
       <c r="H1480">
-        <v>0.009075290917900913</v>
+        <v>0.008901932121838466</v>
       </c>
       <c r="I1480">
-        <v>-0.08007638818734275</v>
+        <v>0.3022646601040799</v>
       </c>
       <c r="J1480">
         <v>1.5547067979184</v>
       </c>
       <c r="K1480">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="L1480">
+        <v>4.68</v>
+      </c>
+      <c r="M1480">
+        <v>2.96</v>
+      </c>
+      <c r="N1480">
         <v>4.3</v>
       </c>
-      <c r="M1480">
-        <v>2.93</v>
-      </c>
-      <c r="N1480">
-        <v>4.52</v>
-      </c>
       <c r="O1480">
         <v>1</v>
       </c>
       <c r="P1480" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="479">
   <si>
     <t>trade_time</t>
   </si>
@@ -706,10 +706,10 @@
     <t>2021-09-17</t>
   </si>
   <si>
-    <t>2021-09-27</t>
+    <t>2021-10-12</t>
   </si>
   <si>
-    <t>2021-10-12</t>
+    <t>2021-11-05</t>
   </si>
   <si>
     <t>2021-10-19</t>
@@ -1060,10 +1060,10 @@
     <t>2021-09-23</t>
   </si>
   <si>
-    <t>2021-09-30</t>
+    <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-10-21</t>
+    <t>2021-11-08</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -1449,6 +1449,9 @@
   <si>
     <t>2021-09-14</t>
   </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
 </sst>
 </file>
 
@@ -75563,40 +75566,40 @@
         <v>230</v>
       </c>
       <c r="C1476">
-        <v>0.9425372818822506</v>
+        <v>0.2571596237574703</v>
       </c>
       <c r="D1476" t="s">
         <v>348</v>
       </c>
       <c r="E1476">
-        <v>0.5892240472995525</v>
+        <v>0.6540780625073239</v>
       </c>
       <c r="F1476">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1476">
-        <v>0.008557462718117749</v>
+        <v>0.008102840376242528</v>
       </c>
       <c r="H1476">
-        <v>0.008870775952700449</v>
+        <v>0.008345921937492676</v>
       </c>
       <c r="I1476">
-        <v>0.3533132345826981</v>
+        <v>0.3969184387498537</v>
       </c>
       <c r="J1476">
         <v>1.281973979164225</v>
       </c>
       <c r="K1476">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="L1476">
-        <v>4.75</v>
+        <v>4.18</v>
       </c>
       <c r="M1476">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="N1476">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="O1476">
         <v>1</v>
@@ -75613,40 +75616,40 @@
         <v>231</v>
       </c>
       <c r="C1477">
-        <v>0.2571596237574703</v>
+        <v>0.3784084347980876</v>
       </c>
       <c r="D1477" t="s">
         <v>349</v>
       </c>
       <c r="E1477">
-        <v>0.6540780625073239</v>
+        <v>0.3268676541730144</v>
       </c>
       <c r="F1477">
         <v>1</v>
       </c>
       <c r="G1477">
-        <v>0.008102840376242528</v>
+        <v>0.007121591565201912</v>
       </c>
       <c r="H1477">
-        <v>0.008345921937492676</v>
+        <v>0.006993132345826986</v>
       </c>
       <c r="I1477">
-        <v>0.3969184387498537</v>
+        <v>-0.05154078062507317</v>
       </c>
       <c r="J1477">
         <v>1.281973979164225</v>
       </c>
       <c r="K1477">
-        <v>3.06</v>
+        <v>2.63</v>
       </c>
       <c r="L1477">
-        <v>4.18</v>
+        <v>3.75</v>
       </c>
       <c r="M1477">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="N1477">
-        <v>4.5</v>
+        <v>3.66</v>
       </c>
       <c r="O1477">
         <v>1</v>
@@ -75660,13 +75663,13 @@
         <v>0</v>
       </c>
       <c r="B1478" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C1478">
         <v>-0.5774028016303054</v>
       </c>
       <c r="D1478" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1478">
         <v>-0.1641203937552014</v>
@@ -75702,7 +75705,7 @@
         <v>1</v>
       </c>
       <c r="P1478" t="s">
-        <v>348</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1479" spans="1:16">
@@ -75716,7 +75719,7 @@
         <v>-0.4852909179009135</v>
       </c>
       <c r="D1479" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1479">
         <v>-0.1641203937552014</v>
@@ -75752,7 +75755,7 @@
         <v>1</v>
       </c>
       <c r="P1479" t="s">
-        <v>348</v>
+        <v>478</v>
       </c>
     </row>
     <row r="1480" spans="1:16">
@@ -75802,7 +75805,7 @@
         <v>1</v>
       </c>
       <c r="P1480" t="s">
-        <v>348</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4455" uniqueCount="479">
   <si>
     <t>trade_time</t>
   </si>
@@ -709,10 +709,10 @@
     <t>2021-10-12</t>
   </si>
   <si>
-    <t>2021-11-05</t>
+    <t>2021-10-19</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-11-08</t>
   </si>
   <si>
     <t>2021-10-26</t>
@@ -1063,7 +1063,7 @@
     <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -1808,7 +1808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1480"/>
+  <dimension ref="A1:P1481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -75616,40 +75616,40 @@
         <v>231</v>
       </c>
       <c r="C1477">
-        <v>0.3784084347980876</v>
+        <v>0.3138162410488201</v>
       </c>
       <c r="D1477" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E1477">
-        <v>0.3268676541730144</v>
+        <v>0.6540780625073239</v>
       </c>
       <c r="F1477">
         <v>1</v>
       </c>
       <c r="G1477">
-        <v>0.007121591565201912</v>
+        <v>0.00782618375895118</v>
       </c>
       <c r="H1477">
-        <v>0.006993132345826986</v>
+        <v>0.008345921937492676</v>
       </c>
       <c r="I1477">
-        <v>-0.05154078062507317</v>
+        <v>0.3402618214585038</v>
       </c>
       <c r="J1477">
         <v>1.281973979164225</v>
       </c>
       <c r="K1477">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="L1477">
-        <v>3.75</v>
+        <v>4.07</v>
       </c>
       <c r="M1477">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="N1477">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
       <c r="O1477">
         <v>1</v>
@@ -75660,63 +75660,63 @@
     </row>
     <row r="1478" spans="1:16">
       <c r="A1478" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1478" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C1478">
-        <v>-0.5774028016303054</v>
+        <v>0.3268676541730144</v>
       </c>
       <c r="D1478" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1478">
-        <v>-0.1641203937552014</v>
+        <v>0.2784084347980875</v>
       </c>
       <c r="F1478">
         <v>1</v>
       </c>
       <c r="G1478">
-        <v>0.008937402801630306</v>
+        <v>0.006993132345826986</v>
       </c>
       <c r="H1478">
-        <v>0.009164120393755202</v>
+        <v>0.007021591565201913</v>
       </c>
       <c r="I1478">
-        <v>0.4132824078751041</v>
+        <v>-0.04845921937492692</v>
       </c>
       <c r="J1478">
-        <v>1.5547067979184</v>
+        <v>1.281973979164225</v>
       </c>
       <c r="K1478">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="L1478">
-        <v>4.18</v>
+        <v>3.66</v>
       </c>
       <c r="M1478">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="N1478">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="O1478">
         <v>1</v>
       </c>
       <c r="P1478" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="1479" spans="1:16">
       <c r="A1479" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1479" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C1479">
-        <v>-0.4852909179009135</v>
+        <v>-0.5774028016303054</v>
       </c>
       <c r="D1479" t="s">
         <v>348</v>
@@ -75728,22 +75728,22 @@
         <v>1</v>
       </c>
       <c r="G1479">
-        <v>0.008625290917900914</v>
+        <v>0.008937402801630306</v>
       </c>
       <c r="H1479">
         <v>0.009164120393755202</v>
       </c>
       <c r="I1479">
-        <v>0.3211705241457121</v>
+        <v>0.4132824078751041</v>
       </c>
       <c r="J1479">
         <v>1.5547067979184</v>
       </c>
       <c r="K1479">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="L1479">
-        <v>4.07</v>
+        <v>4.18</v>
       </c>
       <c r="M1479">
         <v>3</v>
@@ -75760,51 +75760,101 @@
     </row>
     <row r="1480" spans="1:16">
       <c r="A1480" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1480" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C1480">
-        <v>-0.115367306088257</v>
+        <v>-0.4852909179009135</v>
       </c>
       <c r="D1480" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E1480">
-        <v>-0.3019321218384654</v>
+        <v>-0.1641203937552014</v>
       </c>
       <c r="F1480">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1480">
-        <v>0.008715367306088257</v>
+        <v>0.008625290917900914</v>
       </c>
       <c r="H1480">
-        <v>0.008901932121838466</v>
+        <v>0.009164120393755202</v>
       </c>
       <c r="I1480">
-        <v>0.1865648157502084</v>
+        <v>0.3211705241457121</v>
       </c>
       <c r="J1480">
         <v>1.5547067979184</v>
       </c>
       <c r="K1480">
+        <v>2.93</v>
+      </c>
+      <c r="L1480">
+        <v>4.07</v>
+      </c>
+      <c r="M1480">
+        <v>3</v>
+      </c>
+      <c r="N1480">
+        <v>4.5</v>
+      </c>
+      <c r="O1480">
+        <v>1</v>
+      </c>
+      <c r="P1480" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:16">
+      <c r="A1481" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1481">
+        <v>-0.115367306088257</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>350</v>
+      </c>
+      <c r="E1481">
+        <v>-0.3019321218384654</v>
+      </c>
+      <c r="F1481">
+        <v>-1</v>
+      </c>
+      <c r="G1481">
+        <v>0.008715367306088257</v>
+      </c>
+      <c r="H1481">
+        <v>0.008901932121838466</v>
+      </c>
+      <c r="I1481">
+        <v>0.1865648157502084</v>
+      </c>
+      <c r="J1481">
+        <v>1.5547067979184</v>
+      </c>
+      <c r="K1481">
         <v>2.84</v>
       </c>
-      <c r="L1480">
+      <c r="L1481">
         <v>4.3</v>
       </c>
-      <c r="M1480">
+      <c r="M1481">
         <v>2.96</v>
       </c>
-      <c r="N1480">
+      <c r="N1481">
         <v>4.3</v>
       </c>
-      <c r="O1480">
-        <v>1</v>
-      </c>
-      <c r="P1480" t="s">
+      <c r="O1481">
+        <v>1</v>
+      </c>
+      <c r="P1481" t="s">
         <v>478</v>
       </c>
     </row>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1063,7 +1063,7 @@
     <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-11-09</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -75672,7 +75672,7 @@
         <v>349</v>
       </c>
       <c r="E1478">
-        <v>0.2784084347980875</v>
+        <v>0.3109663531312257</v>
       </c>
       <c r="F1478">
         <v>1</v>
@@ -75681,10 +75681,10 @@
         <v>0.006993132345826986</v>
       </c>
       <c r="H1478">
-        <v>0.007021591565201913</v>
+        <v>0.006849033646868774</v>
       </c>
       <c r="I1478">
-        <v>-0.04845921937492692</v>
+        <v>-0.01590130104178877</v>
       </c>
       <c r="J1478">
         <v>1.281973979164225</v>
@@ -75696,10 +75696,10 @@
         <v>3.66</v>
       </c>
       <c r="M1478">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="N1478">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="O1478">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1063,10 +1063,10 @@
     <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-11</t>
   </si>
   <si>
-    <t>2021-11-01</t>
+    <t>2021-11-05</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75672,7 +75672,7 @@
         <v>349</v>
       </c>
       <c r="E1478">
-        <v>0.3109663531312257</v>
+        <v>0.2794255725061521</v>
       </c>
       <c r="F1478">
         <v>1</v>
@@ -75681,10 +75681,10 @@
         <v>0.006993132345826986</v>
       </c>
       <c r="H1478">
-        <v>0.006849033646868774</v>
+        <v>0.006740574427493847</v>
       </c>
       <c r="I1478">
-        <v>-0.01590130104178877</v>
+        <v>-0.04744208166686237</v>
       </c>
       <c r="J1478">
         <v>1.281973979164225</v>
@@ -75696,10 +75696,10 @@
         <v>3.66</v>
       </c>
       <c r="M1478">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="N1478">
-        <v>3.58</v>
+        <v>3.51</v>
       </c>
       <c r="O1478">
         <v>1</v>
@@ -75822,7 +75822,7 @@
         <v>350</v>
       </c>
       <c r="E1481">
-        <v>-0.3019321218384654</v>
+        <v>-0.3388788785253931</v>
       </c>
       <c r="F1481">
         <v>-1</v>
@@ -75831,10 +75831,10 @@
         <v>0.008715367306088257</v>
       </c>
       <c r="H1481">
-        <v>0.008901932121838466</v>
+        <v>0.007838878878525394</v>
       </c>
       <c r="I1481">
-        <v>0.1865648157502084</v>
+        <v>0.2235115724371362</v>
       </c>
       <c r="J1481">
         <v>1.5547067979184</v>
@@ -75846,10 +75846,10 @@
         <v>4.3</v>
       </c>
       <c r="M1481">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="N1481">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O1481">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1063,10 +1063,10 @@
     <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-11-11</t>
+    <t>2021-11-15</t>
   </si>
   <si>
-    <t>2021-11-05</t>
+    <t>2021-11-01</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75672,7 +75672,7 @@
         <v>349</v>
       </c>
       <c r="E1478">
-        <v>0.2794255725061521</v>
+        <v>0.4348032306309322</v>
       </c>
       <c r="F1478">
         <v>1</v>
@@ -75681,10 +75681,10 @@
         <v>0.006993132345826986</v>
       </c>
       <c r="H1478">
-        <v>0.006740574427493847</v>
+        <v>0.006665196769369068</v>
       </c>
       <c r="I1478">
-        <v>-0.04744208166686237</v>
+        <v>0.1079355764579177</v>
       </c>
       <c r="J1478">
         <v>1.281973979164225</v>
@@ -75696,10 +75696,10 @@
         <v>3.66</v>
       </c>
       <c r="M1478">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="N1478">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="O1478">
         <v>1</v>
@@ -75822,7 +75822,7 @@
         <v>350</v>
       </c>
       <c r="E1481">
-        <v>-0.3388788785253931</v>
+        <v>-0.3019321218384654</v>
       </c>
       <c r="F1481">
         <v>-1</v>
@@ -75831,10 +75831,10 @@
         <v>0.008715367306088257</v>
       </c>
       <c r="H1481">
-        <v>0.007838878878525394</v>
+        <v>0.008901932121838466</v>
       </c>
       <c r="I1481">
-        <v>0.2235115724371362</v>
+        <v>0.1865648157502084</v>
       </c>
       <c r="J1481">
         <v>1.5547067979184</v>
@@ -75846,10 +75846,10 @@
         <v>4.3</v>
       </c>
       <c r="M1481">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="N1481">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O1481">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1063,10 +1063,10 @@
     <t>2021-10-21</t>
   </si>
   <si>
-    <t>2021-11-15</t>
+    <t>2021-11-16</t>
   </si>
   <si>
-    <t>2021-11-01</t>
+    <t>2021-11-05</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75672,7 +75672,7 @@
         <v>349</v>
       </c>
       <c r="E1478">
-        <v>0.4348032306309322</v>
+        <v>0.3419834908392905</v>
       </c>
       <c r="F1478">
         <v>1</v>
@@ -75681,10 +75681,10 @@
         <v>0.006993132345826986</v>
       </c>
       <c r="H1478">
-        <v>0.006665196769369068</v>
+        <v>0.006598016509160709</v>
       </c>
       <c r="I1478">
-        <v>0.1079355764579177</v>
+        <v>0.01511583666627603</v>
       </c>
       <c r="J1478">
         <v>1.281973979164225</v>
@@ -75696,10 +75696,10 @@
         <v>3.66</v>
       </c>
       <c r="M1478">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="N1478">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="O1478">
         <v>1</v>
@@ -75822,7 +75822,7 @@
         <v>350</v>
       </c>
       <c r="E1481">
-        <v>-0.3019321218384654</v>
+        <v>-0.3388788785253931</v>
       </c>
       <c r="F1481">
         <v>-1</v>
@@ -75831,10 +75831,10 @@
         <v>0.008715367306088257</v>
       </c>
       <c r="H1481">
-        <v>0.008901932121838466</v>
+        <v>0.007838878878525394</v>
       </c>
       <c r="I1481">
-        <v>0.1865648157502084</v>
+        <v>0.2235115724371362</v>
       </c>
       <c r="J1481">
         <v>1.5547067979184</v>
@@ -75846,10 +75846,10 @@
         <v>4.3</v>
       </c>
       <c r="M1481">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="N1481">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O1481">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1072,10 +1072,10 @@
     <t>2021-11-01</t>
   </si>
   <si>
-    <t>2021-11-23</t>
+    <t>2021-11-24</t>
   </si>
   <si>
-    <t>2021-11-12</t>
+    <t>2021-11-15</t>
   </si>
   <si>
     <t>2016-07-07</t>
@@ -75781,7 +75781,7 @@
         <v>352</v>
       </c>
       <c r="E1480">
-        <v>0.4660821897975014</v>
+        <v>0.4063440112560057</v>
       </c>
       <c r="F1480">
         <v>1</v>
@@ -75790,10 +75790,10 @@
         <v>0.007021591565201913</v>
       </c>
       <c r="H1480">
-        <v>0.006593917810202498</v>
+        <v>0.006713655988743994</v>
       </c>
       <c r="I1480">
-        <v>0.1876737549994139</v>
+        <v>0.1279355764579182</v>
       </c>
       <c r="J1480">
         <v>1.281973979164225</v>
@@ -75805,10 +75805,10 @@
         <v>3.65</v>
       </c>
       <c r="M1480">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="N1480">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="O1480">
         <v>1</v>
@@ -75981,7 +75981,7 @@
         <v>353</v>
       </c>
       <c r="E1484">
-        <v>-0.2934845869208971</v>
+        <v>-0.2279375189417134</v>
       </c>
       <c r="F1484">
         <v>1</v>
@@ -75990,10 +75990,10 @@
         <v>0.007738878878525392</v>
       </c>
       <c r="H1484">
-        <v>0.007293484586920898</v>
+        <v>0.007327937518941713</v>
       </c>
       <c r="I1484">
-        <v>0.1453942916044961</v>
+        <v>0.2109413595836798</v>
       </c>
       <c r="J1484">
         <v>1.5547067979184</v>
@@ -76005,10 +76005,10 @@
         <v>3.65</v>
       </c>
       <c r="M1484">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="N1484">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O1484">
         <v>1</v>

--- a/s60_signal/position-01071-600027.xlsx
+++ b/s60_signal/position-01071-600027.xlsx
@@ -1072,7 +1072,7 @@
     <t>2021-11-01</t>
   </si>
   <si>
-    <t>2021-11-24</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2021-11-15</t>
@@ -75781,7 +75781,7 @@
         <v>352</v>
       </c>
       <c r="E1480">
-        <v>0.4063440112560057</v>
+        <v>0.4719834908392904</v>
       </c>
       <c r="F1480">
         <v>1</v>
@@ -75790,10 +75790,10 @@
         <v>0.007021591565201913</v>
       </c>
       <c r="H1480">
-        <v>0.006713655988743994</v>
+        <v>0.00672801650916071</v>
       </c>
       <c r="I1480">
-        <v>0.1279355764579182</v>
+        <v>0.1935750560412028</v>
       </c>
       <c r="J1480">
         <v>1.281973979164225</v>
@@ -75805,10 +75805,10 @@
         <v>3.65</v>
       </c>
       <c r="M1480">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="N1480">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="O1480">
         <v>1</v>
